--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr checkCompatibility="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\TPI\Documents session 2026\Préparation\4_Documents en ligne\Documents destinés aux candidates et candidats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13CFF3CE-B7E9-4BCF-976F-778AB771C7C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A759646A-3CA7-48E4-982E-305C16FF969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="8" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$83</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -106,6 +106,24 @@
   </si>
   <si>
     <t>Total général &gt;</t>
+  </si>
+  <si>
+    <t>DOC - Context et objectifs du projet</t>
+  </si>
+  <si>
+    <t>DOC - Analyse par domaines de technologies</t>
+  </si>
+  <si>
+    <t>DOC - Analyse des outils d'automatisation</t>
+  </si>
+  <si>
+    <t>DOC - Rentabilité et valeurs ajoutée</t>
+  </si>
+  <si>
+    <t>DOC - Analyse des risques</t>
+  </si>
+  <si>
+    <t>DOC - Sécurité de l'information et protection des données</t>
   </si>
 </sst>
 </file>
@@ -402,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -451,100 +469,108 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1177,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1226,649 +1252,698 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36"/>
-      <c r="B6" s="32"/>
+      <c r="A6" s="26">
+        <v>46153</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>11</v>
+      </c>
       <c r="C6" s="33"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="15"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="15"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="8"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="15"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="8">
+        <v>0.33329999999999999</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="15"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="8">
+        <v>0.33329999999999999</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="15"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="8">
+        <v>0.33329999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="14"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="8"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="14"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="14"/>
+      <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="9">
-        <f>SUM(D6:D10)</f>
+      <c r="D14" s="9">
+        <f>SUM(D6:D11)</f>
+        <v>4.9999000000000011</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="14"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>46154</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="14"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="14"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="8"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="14"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="14"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="8"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="14"/>
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="9">
+        <f>SUM(D16:D20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="15"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="22"/>
-    </row>
-    <row r="13" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="15"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="15"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="15"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
-      <c r="B18" s="2" t="s">
+    <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="14"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="21"/>
+    </row>
+    <row r="23" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="13"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="7"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="14"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="14"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="8"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="14"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="14"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="14"/>
+      <c r="B28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="9">
-        <f>SUM(D13:D17)</f>
+      <c r="D28" s="9">
+        <f>SUM(D23:D27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="22"/>
-    </row>
-    <row r="20" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="15"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="8"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="15"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="15"/>
-      <c r="B25" s="2" t="s">
+    <row r="29" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="14"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21"/>
+    </row>
+    <row r="30" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="13"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="7"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="14"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="14"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="8"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="14"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="14"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="14"/>
+      <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="9">
-        <f>SUM(D20:D24)</f>
+      <c r="D35" s="9">
+        <f>SUM(D30:D34)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="22"/>
-    </row>
-    <row r="27" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="15"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="15"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="15"/>
-      <c r="B32" s="2" t="s">
+    <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="25"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="24"/>
+    </row>
+    <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="13"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="7"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="14"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="14"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="8"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="14"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="14"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="14"/>
+      <c r="B42" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="9">
-        <f>SUM(D27:D31)</f>
+      <c r="D42" s="9">
+        <f>SUM(D37:D41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="26"/>
-    </row>
-    <row r="34" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="15"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="8"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="15"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="8"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
-      <c r="B39" s="2" t="s">
+    <row r="43" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="25"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="24"/>
+    </row>
+    <row r="44" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="13"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="14"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="14"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="8"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="14"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="14"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="14"/>
+      <c r="B49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D39" s="9">
-        <f>SUM(D34:D38)</f>
+      <c r="D49" s="9">
+        <f>SUM(D44:D48)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="26"/>
-    </row>
-    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="14"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="15"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="8"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="15"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="8"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="8"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="15"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="8"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="15"/>
-      <c r="B46" s="2" t="s">
+    <row r="50" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="25"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="24"/>
+    </row>
+    <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="13"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="14"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="14"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="14"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="14"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="14"/>
+      <c r="B56" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="9">
-        <f>SUM(D41:D45)</f>
+      <c r="D56" s="9">
+        <f>SUM(D51:D55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="26"/>
-    </row>
-    <row r="48" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="7"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="15"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="8"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="15"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="8"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="15"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="8"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="15"/>
-      <c r="B52" s="18"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="8"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="15"/>
-      <c r="B53" s="2" t="s">
+    <row r="57" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="25"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="24"/>
+    </row>
+    <row r="58" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="13"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="14"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="8"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="14"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="8"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="14"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="14"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="14"/>
+      <c r="B63" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D53" s="9">
-        <f>SUM(D48:D52)</f>
+      <c r="D63" s="9">
+        <f>SUM(D58:D62)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="26"/>
-    </row>
-    <row r="55" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="14"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="15"/>
-      <c r="B56" s="18"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="15"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="15"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="8"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="15"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="8"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="15"/>
-      <c r="B60" s="2" t="s">
+    <row r="64" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="25"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="24"/>
+    </row>
+    <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="13"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="7"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="14"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="8"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="14"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="8"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="14"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="8"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="14"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="14"/>
+      <c r="B70" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="9">
-        <f>SUM(D55:D59)</f>
+      <c r="D70" s="9">
+        <f>SUM(D65:D69)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="26"/>
-    </row>
-    <row r="62" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="14"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="7"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="15"/>
-      <c r="B63" s="18"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="8"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="15"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="8"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="15"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="8"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="15"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="8"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="15"/>
-      <c r="B67" s="2" t="s">
+    <row r="71" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="14"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="21"/>
+    </row>
+    <row r="72" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="13"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="7"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="14"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="14"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="14"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="14"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="14"/>
+      <c r="B77" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D67" s="9">
-        <f>SUM(D62:D66)</f>
+      <c r="D77" s="9">
+        <f>SUM(D72:D76)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="15"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="22"/>
-    </row>
-    <row r="69" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="14"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="7"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="15"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="8"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="15"/>
-      <c r="B71" s="18"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="8"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="15"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="8"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="15"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="8"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="15"/>
-      <c r="B74" s="2" t="s">
+    <row r="78" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="25"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="24"/>
+    </row>
+    <row r="79" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="13"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="7"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="14"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="14"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="14"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="14"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="14"/>
+      <c r="B84" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D74" s="9">
-        <f>SUM(D69:D73)</f>
+      <c r="D84" s="9">
+        <f>SUM(D79:D83)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
-      <c r="B75" s="24"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="26"/>
-    </row>
-    <row r="76" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="7"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="15"/>
-      <c r="B77" s="18"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="8"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="15"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="8"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="15"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="8"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="15"/>
-      <c r="B80" s="18"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="8"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="15"/>
-      <c r="B81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="9">
-        <f>SUM(D76:D80)</f>
+    <row r="85" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="25"/>
+      <c r="B85" s="22"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="24"/>
+    </row>
+    <row r="86" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="11"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" s="12">
+        <f>D14+D21+D28+D35+D42+D49+D56+D63+D70+D77+D84</f>
+        <v>4.9999000000000011</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="36" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="23"/>
-      <c r="B82" s="24"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="26"/>
-    </row>
-    <row r="83" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="11"/>
-      <c r="B83" s="10"/>
-      <c r="C83" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D83" s="12">
-        <f>D11+D18+D25+D32+D39+D46+D53+D60+D67+D74+D81</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
+      <c r="B87" s="36"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="A20:A26"/>
+  <mergeCells count="85">
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="A55:A61"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B82:D82"/>
-    <mergeCell ref="A69:A75"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A62:A68"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="A48:A54"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A37:A43"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A13:A19"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="A65:A71"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="A44:A50"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A51:A57"/>
+    <mergeCell ref="A72:A78"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="A79:A85"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A58:A64"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="B29:D29"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D11">
+  <conditionalFormatting sqref="D6:D14">
     <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
@@ -1876,92 +1951,92 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D18">
+  <conditionalFormatting sqref="D16:D21">
     <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D13)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D16)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D13)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D25">
+  <conditionalFormatting sqref="D23:D28">
     <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D20)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D23)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D20)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D23)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D27:D32">
+  <conditionalFormatting sqref="D30:D35">
     <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D27)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D30)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D27)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D30)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D34:D39">
+  <conditionalFormatting sqref="D37:D42">
     <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D34)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D37)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D34)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D37)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D41:D46">
+  <conditionalFormatting sqref="D44:D49">
     <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D41)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D44)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D41)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D44)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D48:D53">
+  <conditionalFormatting sqref="D51:D56">
     <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D51)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D48)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D51)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D55:D60">
+  <conditionalFormatting sqref="D58:D63">
     <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D55)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D58)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D55)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D58)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D62:D67">
+  <conditionalFormatting sqref="D65:D70">
     <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D62)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D65)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D62)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D65)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D69:D74">
+  <conditionalFormatting sqref="D72:D77">
     <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D69)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D72)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D69)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D72)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D76:D81">
+  <conditionalFormatting sqref="D79:D84">
     <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D76)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D79)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D76)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D79)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D83">
+  <conditionalFormatting sqref="D86">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D83)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D86)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D83)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D86)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -1973,8 +2048,8 @@
     <oddFooter>&amp;L&amp;8&amp;F&amp;R&amp;8Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="47" max="16383" man="1"/>
-    <brk id="83" max="3" man="1"/>
+    <brk id="50" max="16383" man="1"/>
+    <brk id="86" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A759646A-3CA7-48E4-982E-305C16FF969C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47308637-90E4-49D1-99C9-9B058518078D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="19">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>DOC - Sécurité de l'information et protection des données</t>
+  </si>
+  <si>
+    <t>DOC - Comparaison et choix</t>
+  </si>
+  <si>
+    <t>D'habitude l'analyse me fait des soucis, visiblement les derniers modules ont bien permis de m'habituer à celle-ci.</t>
   </si>
 </sst>
 </file>
@@ -420,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -469,6 +475,18 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -505,6 +523,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -517,52 +539,44 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1214,119 +1228,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="29"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="31"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26">
+      <c r="A6" s="38">
         <v>46153</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="33"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="18"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="14"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="17"/>
+      <c r="B10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="8">
-        <v>0.33329999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="17" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="17"/>
+      <c r="B11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="8">
-        <v>0.33329999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
-      <c r="B11" s="17" t="s">
+      <c r="C11" s="21"/>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="17"/>
+      <c r="B12" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="8">
-        <v>0.33329999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="14"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="8"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="38"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1334,50 +1352,52 @@
         <v>7</v>
       </c>
       <c r="D14" s="9">
-        <f>SUM(D6:D11)</f>
-        <v>4.9999000000000011</v>
+        <f>SUM(D6:D13)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="21"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
+      <c r="A16" s="16">
         <v>46154</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="7"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="14"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="14"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
@@ -1390,43 +1410,43 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="21"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
     </row>
     <row r="23" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="17"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="8"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="17"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="8"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="14"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
+      <c r="A26" s="17"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="17"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
       <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
+      <c r="A28" s="17"/>
       <c r="B28" s="2" t="s">
         <v>8</v>
       </c>
@@ -1439,43 +1459,43 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="14"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="21"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="24"/>
     </row>
     <row r="30" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="16"/>
+      <c r="A30" s="16"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="21"/>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="18"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="14"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="18"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="18"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
       <c r="D34" s="8"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
@@ -1489,42 +1509,42 @@
     </row>
     <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="25"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="24"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
     </row>
     <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="16"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="19"/>
       <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="14"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="21"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="14"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="21"/>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="14"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="18"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="14"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="18"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="14"/>
+      <c r="A42" s="17"/>
       <c r="B42" s="2" t="s">
         <v>8</v>
       </c>
@@ -1538,42 +1558,42 @@
     </row>
     <row r="43" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="25"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="24"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="28"/>
     </row>
     <row r="44" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="16"/>
+      <c r="A44" s="16"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="14"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="18"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="21"/>
       <c r="D45" s="8"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="14"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="18"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="21"/>
       <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="14"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="14"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="2" t="s">
         <v>8</v>
       </c>
@@ -1587,42 +1607,42 @@
     </row>
     <row r="50" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="25"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="24"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="28"/>
     </row>
     <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="13"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="16"/>
+      <c r="A51" s="16"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="19"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="14"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="21"/>
       <c r="D52" s="8"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="14"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="21"/>
       <c r="D53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="14"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="14"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="21"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="14"/>
+      <c r="A56" s="17"/>
       <c r="B56" s="2" t="s">
         <v>8</v>
       </c>
@@ -1636,42 +1656,42 @@
     </row>
     <row r="57" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="25"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="24"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="28"/>
     </row>
     <row r="58" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="13"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="16"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="19"/>
       <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="14"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="21"/>
       <c r="D59" s="8"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="14"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="21"/>
       <c r="D60" s="8"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="14"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="18"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
       <c r="D61" s="8"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="14"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="21"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="14"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="2" t="s">
         <v>8</v>
       </c>
@@ -1685,42 +1705,42 @@
     </row>
     <row r="64" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="25"/>
-      <c r="B64" s="22"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="24"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="28"/>
     </row>
     <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="13"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="16"/>
+      <c r="A65" s="16"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="19"/>
       <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="14"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="21"/>
       <c r="D66" s="8"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="21"/>
       <c r="D67" s="8"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="14"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="18"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="21"/>
       <c r="D68" s="8"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="14"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="21"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="14"/>
+      <c r="A70" s="17"/>
       <c r="B70" s="2" t="s">
         <v>8</v>
       </c>
@@ -1733,43 +1753,43 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="14"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="21"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="24"/>
     </row>
     <row r="72" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="13"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="16"/>
+      <c r="A72" s="16"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="19"/>
       <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="14"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="18"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="21"/>
       <c r="D73" s="8"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="14"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="18"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="21"/>
       <c r="D74" s="8"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="14"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="21"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="21"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="14"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="2" t="s">
         <v>8</v>
       </c>
@@ -1783,42 +1803,42 @@
     </row>
     <row r="78" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="25"/>
-      <c r="B78" s="22"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="24"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="28"/>
     </row>
     <row r="79" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="13"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="16"/>
+      <c r="A79" s="16"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="19"/>
       <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="14"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="18"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="21"/>
       <c r="D80" s="8"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="14"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="21"/>
       <c r="D81" s="8"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="14"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="18"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="21"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="14"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="18"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="21"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="14"/>
+      <c r="A84" s="17"/>
       <c r="B84" s="2" t="s">
         <v>8</v>
       </c>
@@ -1832,9 +1852,9 @@
     </row>
     <row r="85" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="25"/>
-      <c r="B85" s="22"/>
-      <c r="C85" s="23"/>
-      <c r="D85" s="24"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="28"/>
     </row>
     <row r="86" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11"/>
@@ -1844,19 +1864,87 @@
       </c>
       <c r="D86" s="12">
         <f>D14+D21+D28+D35+D42+D49+D56+D63+D70+D77+D84</f>
-        <v>4.9999000000000011</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="36" t="s">
+      <c r="A87" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B87" s="36"/>
-      <c r="C87" s="36"/>
-      <c r="D87" s="36"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="15"/>
+      <c r="D87" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="85">
+  <mergeCells count="84">
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A58:A64"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="A79:A85"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="A72:A78"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="A65:A71"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="A44:A50"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A51:A57"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A87:D87"/>
     <mergeCell ref="A16:A22"/>
     <mergeCell ref="B16:C16"/>
@@ -1873,75 +1961,6 @@
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="A37:A43"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="A65:A71"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="A44:A50"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="A51:A57"/>
-    <mergeCell ref="A72:A78"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="A79:A85"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="A58:A64"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:D29"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D14">
     <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="Terminé">

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47308637-90E4-49D1-99C9-9B058518078D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF1A169-8DE8-4FA7-AF96-7E2163A72C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -130,6 +130,15 @@
   </si>
   <si>
     <t>D'habitude l'analyse me fait des soucis, visiblement les derniers modules ont bien permis de m'habituer à celle-ci.</t>
+  </si>
+  <si>
+    <t>Préparation au rendez-vous expert</t>
+  </si>
+  <si>
+    <t>DOC - Exigences techniques et fonctionnelles</t>
+  </si>
+  <si>
+    <t>DOC - Concept d'implémentation</t>
   </si>
 </sst>
 </file>
@@ -483,108 +492,108 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1228,107 +1237,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
+      <c r="A6" s="28">
         <v>46153</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="37"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="21"/>
+      <c r="C7" s="20"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="17"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="21"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="17"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="21"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="17"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="13" t="s">
         <v>16</v>
       </c>
@@ -1338,13 +1347,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="17"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
@@ -1357,47 +1366,59 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="15">
         <v>46154</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="7"/>
+      <c r="B16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="7">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="8"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="17"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="8"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="17"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="2" t="s">
         <v>8</v>
       </c>
@@ -1406,47 +1427,47 @@
       </c>
       <c r="D21" s="9">
         <f>SUM(D16:D20)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23"/>
     </row>
     <row r="23" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="16"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="21"/>
+      <c r="A24" s="16"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="8"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="17"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
+      <c r="A25" s="16"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="8"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
+      <c r="A27" s="16"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="17"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="2" t="s">
         <v>8</v>
       </c>
@@ -1459,43 +1480,43 @@
       </c>
     </row>
     <row r="29" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="24"/>
+      <c r="A29" s="16"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23"/>
     </row>
     <row r="30" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="7"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="21"/>
+      <c r="A31" s="16"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="17"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="21"/>
+      <c r="A32" s="16"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="8"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="21"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="17"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="21"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="8"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
+      <c r="A35" s="16"/>
       <c r="B35" s="2" t="s">
         <v>8</v>
       </c>
@@ -1508,43 +1529,43 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="25"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
+      <c r="A36" s="27"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="26"/>
     </row>
     <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="16"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="19"/>
+      <c r="A37" s="15"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="17"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="21"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="21"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="17"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="21"/>
+      <c r="A40" s="16"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="17"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="21"/>
+      <c r="A41" s="16"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="17"/>
+      <c r="A42" s="16"/>
       <c r="B42" s="2" t="s">
         <v>8</v>
       </c>
@@ -1557,43 +1578,43 @@
       </c>
     </row>
     <row r="43" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="25"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="28"/>
+      <c r="A43" s="27"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="26"/>
     </row>
     <row r="44" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="16"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="17"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="21"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="20"/>
       <c r="D45" s="8"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="17"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="21"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="21"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="20"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="17"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="20"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="2" t="s">
         <v>8</v>
       </c>
@@ -1606,43 +1627,43 @@
       </c>
     </row>
     <row r="50" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="25"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="28"/>
+      <c r="A50" s="27"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="26"/>
     </row>
     <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="16"/>
-      <c r="B51" s="18"/>
-      <c r="C51" s="19"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18"/>
       <c r="D51" s="7"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="17"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="21"/>
+      <c r="A52" s="16"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="8"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="21"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="17"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="21"/>
+      <c r="A54" s="16"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="20"/>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="20"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="17"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="2" t="s">
         <v>8</v>
       </c>
@@ -1655,43 +1676,43 @@
       </c>
     </row>
     <row r="57" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="25"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="28"/>
+      <c r="A57" s="27"/>
+      <c r="B57" s="24"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="26"/>
     </row>
     <row r="58" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="16"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="19"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="18"/>
       <c r="D58" s="7"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="17"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="21"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="20"/>
       <c r="D59" s="8"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="17"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="21"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="20"/>
       <c r="D60" s="8"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="17"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="21"/>
+      <c r="A61" s="16"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="20"/>
       <c r="D61" s="8"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="17"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="20"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="17"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="2" t="s">
         <v>8</v>
       </c>
@@ -1704,43 +1725,43 @@
       </c>
     </row>
     <row r="64" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="25"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="28"/>
+      <c r="A64" s="27"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="26"/>
     </row>
     <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="16"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="19"/>
+      <c r="A65" s="15"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="18"/>
       <c r="D65" s="7"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="17"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="21"/>
+      <c r="A66" s="16"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="20"/>
       <c r="D66" s="8"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="17"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="21"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="20"/>
       <c r="D67" s="8"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="17"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="21"/>
+      <c r="A68" s="16"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="20"/>
       <c r="D68" s="8"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="17"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="21"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="20"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="17"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="2" t="s">
         <v>8</v>
       </c>
@@ -1753,43 +1774,43 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="17"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="23"/>
-      <c r="D71" s="24"/>
+      <c r="A71" s="16"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="22"/>
+      <c r="D71" s="23"/>
     </row>
     <row r="72" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="16"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="19"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
       <c r="D72" s="7"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="17"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="21"/>
+      <c r="A73" s="16"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="20"/>
       <c r="D73" s="8"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="17"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="21"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="8"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="17"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="21"/>
+      <c r="A75" s="16"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="20"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="17"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="21"/>
+      <c r="A76" s="16"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="17"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="2" t="s">
         <v>8</v>
       </c>
@@ -1802,43 +1823,43 @@
       </c>
     </row>
     <row r="78" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="25"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="28"/>
+      <c r="A78" s="27"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="26"/>
     </row>
     <row r="79" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="16"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="19"/>
+      <c r="A79" s="15"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="18"/>
       <c r="D79" s="7"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="17"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="21"/>
+      <c r="A80" s="16"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="20"/>
       <c r="D80" s="8"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="17"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="21"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="8"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="17"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="21"/>
+      <c r="A82" s="16"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="17"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="21"/>
+      <c r="A83" s="16"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="20"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="17"/>
+      <c r="A84" s="16"/>
       <c r="B84" s="2" t="s">
         <v>8</v>
       </c>
@@ -1851,10 +1872,10 @@
       </c>
     </row>
     <row r="85" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="25"/>
-      <c r="B85" s="26"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="28"/>
+      <c r="A85" s="27"/>
+      <c r="B85" s="24"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="26"/>
     </row>
     <row r="86" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="11"/>
@@ -1864,53 +1885,53 @@
       </c>
       <c r="D86" s="12">
         <f>D14+D21+D28+D35+D42+D49+D56+D63+D70+D77+D84</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
+      <c r="A87" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B87" s="15"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="15"/>
+      <c r="B87" s="40"/>
+      <c r="C87" s="40"/>
+      <c r="D87" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="A58:A64"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="A79:A85"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="A72:A78"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A16:A22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="B43:D43"/>
     <mergeCell ref="A65:A71"/>
     <mergeCell ref="B65:C65"/>
@@ -1927,40 +1948,40 @@
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="A51:A57"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="A37:A43"/>
+    <mergeCell ref="A72:A78"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="A79:A85"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A58:A64"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:D29"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D14">
     <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="Terminé">

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF1A169-8DE8-4FA7-AF96-7E2163A72C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4998C6-E411-45DA-B6FF-1C3E8AFC94E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$86</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,39 +39,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
-  </si>
-  <si>
-    <r>
-      <t>Projet :</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">[Titre du projet]      </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">                      </t>
-    </r>
-  </si>
-  <si>
-    <t>[Nom Prénom du candidat]</t>
   </si>
   <si>
     <t>Date</t>
@@ -100,9 +67,6 @@
       </rPr>
       <t>↓↓↓</t>
     </r>
-  </si>
-  <si>
-    <t>[no candidat]</t>
   </si>
   <si>
     <t>Total général &gt;</t>
@@ -139,6 +103,42 @@
   </si>
   <si>
     <t>DOC - Concept d'implémentation</t>
+  </si>
+  <si>
+    <r>
+      <t>Projet :</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Automatisation sur un cluster Proxmox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">      </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">                      </t>
+    </r>
+  </si>
+  <si>
+    <t>Voeffray Lucielle</t>
+  </si>
+  <si>
+    <t>PV - Premier rendez-vous expert</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -492,6 +492,10 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -528,6 +532,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -540,8 +548,40 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -556,44 +596,12 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1226,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1237,109 +1245,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+    </row>
+    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="4">
+        <v>157443</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-    </row>
-    <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="B4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="6" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28">
+      <c r="A6" s="38">
         <v>46153</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="37"/>
+      <c r="B6" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="35"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="16"/>
-      <c r="B7" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="20"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="21"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
-      <c r="B8" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="20"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="21"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="16"/>
-      <c r="B9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="20"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="21"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="20"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="21"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="16"/>
-      <c r="B11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="20"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="21"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="16"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="13" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="8">
@@ -1347,18 +1355,18 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14" s="9">
         <f>SUM(D6:D13)</f>
@@ -1366,559 +1374,611 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="15">
+      <c r="A16" s="16">
         <v>46154</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="18"/>
+      <c r="B16" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="19"/>
       <c r="D16" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="16"/>
-      <c r="B17" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="20"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="21"/>
       <c r="D17" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="16"/>
-      <c r="B18" s="19" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="17"/>
+      <c r="B19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="16"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="8"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
       <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="16"/>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="A21" s="17"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="17"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="17"/>
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="9">
+        <f>SUM(D16:D22)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="17"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
+    </row>
+    <row r="25" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="16"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="17"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="8"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="17"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="17"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="8"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="17"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="17"/>
+      <c r="B30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="9">
+        <f>SUM(D25:D29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="24"/>
+    </row>
+    <row r="32" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="16"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="7"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="17"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="8"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="17"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="8"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="17"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="8"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="17"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="8"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="17"/>
+      <c r="B37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="9">
+        <f>SUM(D32:D36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="25"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="28"/>
+    </row>
+    <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="16"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="7"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="17"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="8"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="17"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="8"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="17"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="8"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="17"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="8"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="17"/>
+      <c r="B44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="9">
+        <f>SUM(D39:D43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="25"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="28"/>
+    </row>
+    <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="16"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="7"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="17"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="17"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="17"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="17"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="17"/>
+      <c r="B51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="9">
+        <f>SUM(D46:D50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="25"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="28"/>
+    </row>
+    <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="16"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="17"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="17"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="17"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="17"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="8"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="17"/>
+      <c r="B58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="9">
+        <f>SUM(D53:D57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="25"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="28"/>
+    </row>
+    <row r="60" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="16"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="17"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="17"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="17"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="8"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="17"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="8"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="17"/>
+      <c r="B65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="9">
+        <f>SUM(D60:D64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="25"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="28"/>
+    </row>
+    <row r="67" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="16"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="7"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="17"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="8"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="17"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="17"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="8"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="17"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="17"/>
+      <c r="B72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="9">
+        <f>SUM(D67:D71)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="17"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="24"/>
+    </row>
+    <row r="74" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="16"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="7"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="17"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="17"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="17"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="21"/>
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="17"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="17"/>
+      <c r="B79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="9">
+        <f>SUM(D74:D78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="25"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="28"/>
+    </row>
+    <row r="81" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="16"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="7"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="17"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="17"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="17"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="21"/>
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="17"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="17"/>
+      <c r="B86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="9">
+        <f>SUM(D81:D85)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="25"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="27"/>
+      <c r="D87" s="28"/>
+    </row>
+    <row r="88" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="11"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="9">
-        <f>SUM(D16:D20)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="23"/>
-    </row>
-    <row r="23" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="16"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="8"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="16"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="8"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="16"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="16"/>
-      <c r="B28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="9">
-        <f>SUM(D23:D27)</f>
+      <c r="D88" s="12">
+        <f>D14+D23+D30+D37+D44+D51+D58+D65+D72+D79+D86</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="15" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="16"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="23"/>
-    </row>
-    <row r="30" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="16"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="8"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="16"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="8"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="16"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="8"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="16"/>
-      <c r="B35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="9">
-        <f>SUM(D30:D34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="27"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="26"/>
-    </row>
-    <row r="37" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="15"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="7"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="16"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="16"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="8"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="16"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="8"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="16"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="16"/>
-      <c r="B42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="9">
-        <f>SUM(D37:D41)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="27"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="26"/>
-    </row>
-    <row r="44" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="15"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="16"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="8"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="16"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="8"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="16"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="8"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="16"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="8"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="16"/>
-      <c r="B49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="9">
-        <f>SUM(D44:D48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="27"/>
-      <c r="B50" s="24"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="26"/>
-    </row>
-    <row r="51" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="15"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="7"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="16"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="8"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="16"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="8"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="16"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="8"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="16"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="8"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="16"/>
-      <c r="B56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="9">
-        <f>SUM(D51:D55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="27"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="26"/>
-    </row>
-    <row r="58" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="15"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="7"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="16"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="8"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="16"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="8"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="16"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="8"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="16"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="8"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="16"/>
-      <c r="B63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="9">
-        <f>SUM(D58:D62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="27"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="26"/>
-    </row>
-    <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="15"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="7"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="16"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="8"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="16"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="8"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="16"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="8"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="16"/>
-      <c r="B69" s="19"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="8"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="16"/>
-      <c r="B70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="9">
-        <f>SUM(D65:D69)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="16"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="23"/>
-    </row>
-    <row r="72" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="15"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="7"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="16"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="8"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="16"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="8"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="16"/>
-      <c r="B75" s="19"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="8"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="16"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="8"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="16"/>
-      <c r="B77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="9">
-        <f>SUM(D72:D76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="27"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="26"/>
-    </row>
-    <row r="79" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="15"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="7"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="16"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="8"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="16"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="8"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="16"/>
-      <c r="B82" s="19"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="8"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="16"/>
-      <c r="B83" s="19"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="8"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="16"/>
-      <c r="B84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="9">
-        <f>SUM(D79:D83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="27"/>
-      <c r="B85" s="24"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="26"/>
-    </row>
-    <row r="86" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="11"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D86" s="12">
-        <f>D14+D21+D28+D35+D42+D49+D56+D63+D70+D77+D84</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B87" s="40"/>
-      <c r="C87" s="40"/>
-      <c r="D87" s="40"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="15"/>
+      <c r="D89" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A16:A22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
+  <mergeCells count="86">
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="A37:A43"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -1927,61 +1987,27 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="A65:A71"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="A44:A50"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="A51:A57"/>
-    <mergeCell ref="A72:A78"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="A79:A85"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="A58:A64"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="A39:A45"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D14">
     <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="Terminé">
@@ -1991,7 +2017,7 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D21">
+  <conditionalFormatting sqref="D16:D23">
     <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D16)))</formula>
     </cfRule>
@@ -1999,84 +2025,84 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D16)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D23:D28">
+  <conditionalFormatting sqref="D25:D30">
     <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D23)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D25)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D23)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D30:D35">
+  <conditionalFormatting sqref="D32:D37">
     <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D32)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D30)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D32)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D37:D42">
+  <conditionalFormatting sqref="D39:D44">
     <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D37)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D39)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D37)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D39)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D44:D49">
+  <conditionalFormatting sqref="D46:D51">
     <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D44)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D46)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D44)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D46)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D51:D56">
+  <conditionalFormatting sqref="D53:D58">
     <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D51)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D53)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D51)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D53)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D58:D63">
+  <conditionalFormatting sqref="D60:D65">
     <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D58)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D60)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D58)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D60)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D65:D70">
+  <conditionalFormatting sqref="D67:D72">
     <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D65)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D67)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D65)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D67)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D72:D77">
+  <conditionalFormatting sqref="D74:D79">
     <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D72)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D74)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D72)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D74)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D79:D84">
+  <conditionalFormatting sqref="D81:D86">
     <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D79)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D81)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D79)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D81)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D86">
+  <conditionalFormatting sqref="D88">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D86)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D88)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D86)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D88)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2088,8 +2114,8 @@
     <oddFooter>&amp;L&amp;8&amp;F&amp;R&amp;8Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="50" max="16383" man="1"/>
-    <brk id="86" max="3" man="1"/>
+    <brk id="52" max="16383" man="1"/>
+    <brk id="88" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr checkCompatibility="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE4998C6-E411-45DA-B6FF-1C3E8AFC94E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81893642-EF7A-4F4D-ABFC-2624FC897225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -139,6 +139,18 @@
   </si>
   <si>
     <t>PV - Premier rendez-vous expert</t>
+  </si>
+  <si>
+    <t>Je n'ai pas rencontré de problèmes durant cette demi journée. La rencontre experts m'a bien permis de me mettre en confiance, les experts semblent très sympa et tou devrait biewn se passer.</t>
+  </si>
+  <si>
+    <t>SCHEMA - ProxMox</t>
+  </si>
+  <si>
+    <t>DOC - Concept de formation</t>
+  </si>
+  <si>
+    <t>DOC - Concept de tests</t>
   </si>
 </sst>
 </file>
@@ -492,145 +504,123 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1245,107 +1235,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
+      <c r="A6" s="30">
         <v>46153</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="21"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="17"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="22"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="21"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="17"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="21"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="17"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="13" t="s">
         <v>13</v>
       </c>
@@ -1355,13 +1345,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1374,75 +1364,72 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="17">
         <v>46154</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="22"/>
       <c r="D17" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="17"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="22"/>
       <c r="D18" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="17"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="8"/>
+      <c r="A20" s="18"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="16"/>
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1455,43 +1442,59 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="24"/>
+      <c r="D24" s="25"/>
     </row>
     <row r="25" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="7"/>
+      <c r="A25" s="17">
+        <v>46157</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="8"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="8"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="17"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="21"/>
+      <c r="A28" s="18"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="22"/>
       <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="21"/>
+      <c r="A29" s="18"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="22"/>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="17"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -1500,47 +1503,47 @@
       </c>
       <c r="D30" s="9">
         <f>SUM(D25:D29)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24"/>
+      <c r="A31" s="18"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
     </row>
     <row r="32" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="19"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="21"/>
+      <c r="A33" s="18"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="22"/>
       <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="17"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="21"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="8"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="21"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
       <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="17"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="21"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="17"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="2" t="s">
         <v>6</v>
       </c>
@@ -1553,43 +1556,43 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="25"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="26"/>
       <c r="C38" s="27"/>
       <c r="D38" s="28"/>
     </row>
     <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="16"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="17"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="21"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="22"/>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="17"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="21"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="22"/>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="17"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="21"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="22"/>
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="17"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="21"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="22"/>
       <c r="D43" s="8"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="17"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
@@ -1602,43 +1605,43 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="26"/>
       <c r="C45" s="27"/>
       <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="16"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="21"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="17"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="22"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="21"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="22"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="17"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="21"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="22"/>
       <c r="D50" s="8"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="17"/>
+      <c r="A51" s="18"/>
       <c r="B51" s="2" t="s">
         <v>6</v>
       </c>
@@ -1651,43 +1654,43 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="25"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="26"/>
       <c r="C52" s="27"/>
       <c r="D52" s="28"/>
     </row>
     <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="16"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="19"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="17"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="21"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22"/>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="22"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="17"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="21"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="22"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="17"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="21"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="22"/>
       <c r="D57" s="8"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="17"/>
+      <c r="A58" s="18"/>
       <c r="B58" s="2" t="s">
         <v>6</v>
       </c>
@@ -1700,43 +1703,43 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="25"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="26"/>
       <c r="C59" s="27"/>
       <c r="D59" s="28"/>
     </row>
     <row r="60" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="16"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="19"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="19"/>
+      <c r="C60" s="20"/>
       <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="17"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="21"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="22"/>
       <c r="D61" s="8"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="17"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="22"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="17"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="21"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="22"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="17"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="21"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="22"/>
       <c r="D64" s="8"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="17"/>
+      <c r="A65" s="18"/>
       <c r="B65" s="2" t="s">
         <v>6</v>
       </c>
@@ -1749,43 +1752,43 @@
       </c>
     </row>
     <row r="66" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="25"/>
+      <c r="A66" s="29"/>
       <c r="B66" s="26"/>
       <c r="C66" s="27"/>
       <c r="D66" s="28"/>
     </row>
     <row r="67" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="16"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="19"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="20"/>
       <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="17"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="21"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="22"/>
       <c r="D68" s="8"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="17"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="21"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="22"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="17"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="21"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="22"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="17"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="21"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="22"/>
       <c r="D71" s="8"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="17"/>
+      <c r="A72" s="18"/>
       <c r="B72" s="2" t="s">
         <v>6</v>
       </c>
@@ -1798,43 +1801,43 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="17"/>
-      <c r="B73" s="22"/>
-      <c r="C73" s="23"/>
-      <c r="D73" s="24"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="25"/>
     </row>
     <row r="74" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="16"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="19"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="17"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="21"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="22"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="17"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="21"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="22"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="17"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="21"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="22"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="17"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="21"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="22"/>
       <c r="D78" s="8"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="17"/>
+      <c r="A79" s="18"/>
       <c r="B79" s="2" t="s">
         <v>6</v>
       </c>
@@ -1847,43 +1850,43 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="25"/>
+      <c r="A80" s="29"/>
       <c r="B80" s="26"/>
       <c r="C80" s="27"/>
       <c r="D80" s="28"/>
     </row>
     <row r="81" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="16"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="19"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="20"/>
       <c r="D81" s="7"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="17"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="21"/>
+      <c r="A82" s="18"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="22"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="17"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="21"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="22"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="17"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="21"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="22"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="17"/>
-      <c r="B85" s="20"/>
-      <c r="C85" s="21"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="22"/>
       <c r="D85" s="8"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="17"/>
+      <c r="A86" s="18"/>
       <c r="B86" s="2" t="s">
         <v>6</v>
       </c>
@@ -1896,7 +1899,7 @@
       </c>
     </row>
     <row r="87" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25"/>
+      <c r="A87" s="29"/>
       <c r="B87" s="26"/>
       <c r="C87" s="27"/>
       <c r="D87" s="28"/>
@@ -1909,55 +1912,53 @@
       </c>
       <c r="D88" s="12">
         <f>D14+D23+D30+D37+D44+D51+D58+D65+D72+D79+D86</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
+      <c r="A89" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
+      <c r="B89" s="42"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B80:D80"/>
+  <mergeCells count="85">
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="A67:A73"/>
     <mergeCell ref="B67:C67"/>
@@ -1974,55 +1975,48 @@
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="A53:A59"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A16:A24"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A32:A38"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:D31"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D14">
-    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="Terminé">
+  <conditionalFormatting sqref="D6:D14 D16:D19 D21:D23 D25">
+    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:D23">
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D16)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25:D30">

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81893642-EF7A-4F4D-ABFC-2624FC897225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B59FD28-21C8-4444-AEF2-D12B3D4AF60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$88</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$95</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -152,6 +152,27 @@
   <si>
     <t>DOC - Concept de tests</t>
   </si>
+  <si>
+    <t>Recherche d'info gestion IP</t>
+  </si>
+  <si>
+    <t>DOC - Moyens nécessaires</t>
+  </si>
+  <si>
+    <t>DOC - Structure de la codebase</t>
+  </si>
+  <si>
+    <t>Câblage du RACK</t>
+  </si>
+  <si>
+    <t>Configurer IPMI</t>
+  </si>
+  <si>
+    <t>Installation OS - Problème et solution détaillée au point 6.1.1</t>
+  </si>
+  <si>
+    <t>Installation Cluster</t>
+  </si>
 </sst>
 </file>
 
@@ -161,7 +182,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -221,6 +242,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -447,7 +474,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -504,6 +531,110 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -512,108 +643,20 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -848,7 +891,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -859,7 +902,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1224,7 +1267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1235,107 +1278,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="35"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30">
+      <c r="A6" s="38">
         <v>46153</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="39"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="17"/>
+      <c r="B7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="17"/>
+      <c r="B8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="22"/>
+      <c r="C8" s="21"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="17"/>
+      <c r="B9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="21"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="13" t="s">
         <v>13</v>
       </c>
@@ -1345,13 +1388,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="32"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1364,72 +1407,72 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="23" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="17">
+      <c r="A16" s="16">
         <v>46154</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="21" t="s">
+      <c r="A17" s="17"/>
+      <c r="B17" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="21" t="s">
+      <c r="A18" s="17"/>
+      <c r="B18" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="22"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="21" t="s">
+      <c r="A19" s="17"/>
+      <c r="B19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="22"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
+      <c r="A20" s="17"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="16"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="22"/>
+      <c r="A22" s="17"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1442,108 +1485,129 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="23" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="24"/>
     </row>
     <row r="25" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="17">
+      <c r="A25" s="16">
         <v>46157</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="21" t="s">
+      <c r="A26" s="17"/>
+      <c r="B26" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="22"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="21" t="s">
+      <c r="A27" s="17"/>
+      <c r="B27" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="22"/>
+      <c r="C27" s="21"/>
       <c r="D27" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="17"/>
+      <c r="B28" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="8"/>
-    </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="8"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="21"/>
+      <c r="D29" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="9">
-        <f>SUM(D25:D29)</f>
+      <c r="A30" s="17"/>
+      <c r="B30" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="44"/>
+      <c r="D30" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="17"/>
+      <c r="B31" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="44"/>
+      <c r="D31" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="17"/>
+      <c r="B32" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="44"/>
+      <c r="D32" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="17"/>
+      <c r="B33" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="46"/>
+      <c r="D33" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="17"/>
+      <c r="B34" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="44"/>
+      <c r="D34" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-    </row>
-    <row r="32" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="17"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="18"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="8"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="18"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="8"/>
-    </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="22"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="44"/>
       <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="22"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="44"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="18"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="2" t="s">
         <v>6</v>
       </c>
@@ -1551,48 +1615,48 @@
         <v>5</v>
       </c>
       <c r="D37" s="9">
-        <f>SUM(D32:D36)</f>
-        <v>0</v>
+        <f>SUM(D25:D36)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="28"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="24"/>
     </row>
     <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="17"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="7"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="22"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="21"/>
       <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="18"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="22"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="21"/>
       <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="18"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="22"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="21"/>
       <c r="D42" s="8"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="22"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="21"/>
       <c r="D43" s="8"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
+      <c r="A44" s="17"/>
       <c r="B44" s="2" t="s">
         <v>6</v>
       </c>
@@ -1605,43 +1669,43 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="29"/>
+      <c r="A45" s="25"/>
       <c r="B45" s="26"/>
       <c r="C45" s="27"/>
       <c r="D45" s="28"/>
     </row>
     <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="17"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="20"/>
+      <c r="A46" s="16"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="22"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="18"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="22"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="21"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="18"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="22"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="21"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="18"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="22"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="21"/>
       <c r="D50" s="8"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="18"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="2" t="s">
         <v>6</v>
       </c>
@@ -1654,43 +1718,43 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="29"/>
+      <c r="A52" s="25"/>
       <c r="B52" s="26"/>
       <c r="C52" s="27"/>
       <c r="D52" s="28"/>
     </row>
     <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="17"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="20"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
       <c r="D53" s="7"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="18"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="22"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="21"/>
       <c r="D54" s="8"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="18"/>
-      <c r="B55" s="21"/>
-      <c r="C55" s="22"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="21"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="18"/>
-      <c r="B56" s="21"/>
-      <c r="C56" s="22"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="21"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="18"/>
-      <c r="B57" s="21"/>
-      <c r="C57" s="22"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="21"/>
       <c r="D57" s="8"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="18"/>
+      <c r="A58" s="17"/>
       <c r="B58" s="2" t="s">
         <v>6</v>
       </c>
@@ -1703,43 +1767,43 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="29"/>
+      <c r="A59" s="25"/>
       <c r="B59" s="26"/>
       <c r="C59" s="27"/>
       <c r="D59" s="28"/>
     </row>
     <row r="60" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="17"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="20"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="19"/>
       <c r="D60" s="7"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="18"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="22"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="21"/>
       <c r="D61" s="8"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="18"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="22"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="21"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="18"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="22"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="21"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="18"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="22"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="21"/>
       <c r="D64" s="8"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="18"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="2" t="s">
         <v>6</v>
       </c>
@@ -1752,43 +1816,43 @@
       </c>
     </row>
     <row r="66" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="29"/>
+      <c r="A66" s="25"/>
       <c r="B66" s="26"/>
       <c r="C66" s="27"/>
       <c r="D66" s="28"/>
     </row>
     <row r="67" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="17"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="20"/>
+      <c r="A67" s="16"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="19"/>
       <c r="D67" s="7"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="18"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="22"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="21"/>
       <c r="D68" s="8"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="18"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="22"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="21"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="18"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="22"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="21"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="18"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="22"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="21"/>
       <c r="D71" s="8"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="18"/>
+      <c r="A72" s="17"/>
       <c r="B72" s="2" t="s">
         <v>6</v>
       </c>
@@ -1801,43 +1865,43 @@
       </c>
     </row>
     <row r="73" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="18"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="25"/>
+      <c r="A73" s="25"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="27"/>
+      <c r="D73" s="28"/>
     </row>
     <row r="74" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="17"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="20"/>
+      <c r="A74" s="16"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="19"/>
       <c r="D74" s="7"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="18"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="22"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="21"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="18"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="22"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="21"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="18"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="22"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="21"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="18"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="22"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="21"/>
       <c r="D78" s="8"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="18"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="2" t="s">
         <v>6</v>
       </c>
@@ -1850,43 +1914,43 @@
       </c>
     </row>
     <row r="80" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="29"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="28"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="22"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="24"/>
     </row>
     <row r="81" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="17"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="20"/>
+      <c r="A81" s="16"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="19"/>
       <c r="D81" s="7"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="18"/>
-      <c r="B82" s="21"/>
-      <c r="C82" s="22"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="21"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="18"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="22"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="21"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="18"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="22"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="21"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="18"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="22"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="21"/>
       <c r="D85" s="8"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="18"/>
+      <c r="A86" s="17"/>
       <c r="B86" s="2" t="s">
         <v>6</v>
       </c>
@@ -1899,53 +1963,144 @@
       </c>
     </row>
     <row r="87" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="29"/>
+      <c r="A87" s="25"/>
       <c r="B87" s="26"/>
       <c r="C87" s="27"/>
       <c r="D87" s="28"/>
     </row>
-    <row r="88" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="11"/>
-      <c r="B88" s="10"/>
-      <c r="C88" s="3" t="s">
+    <row r="88" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="16"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="7"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="17"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="8"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="17"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="8"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="17"/>
+      <c r="B91" s="20"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="8"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="17"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="17"/>
+      <c r="B93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="9">
+        <f>SUM(D88:D92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="25"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="27"/>
+      <c r="D94" s="28"/>
+    </row>
+    <row r="95" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="11"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D88" s="12">
-        <f>D14+D23+D30+D37+D44+D51+D58+D65+D72+D79+D86</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="42" t="s">
+      <c r="D95" s="12">
+        <f>D14+D23+D37+D44+D51+D58+D65+D72+D79+D86+D93</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B89" s="42"/>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="85">
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A16:A24"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A32:A38"/>
+  <mergeCells count="92">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="A25:A38"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
@@ -1954,72 +2109,39 @@
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A39:A45"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B73:D73"/>
     <mergeCell ref="A46:A52"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:D31"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D14 D16:D19 D21:D23 D25">
-    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="21" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25:D30">
+  <conditionalFormatting sqref="D25 D6:D14 D16:D19 D21:D23">
+    <cfRule type="containsText" dxfId="20" priority="23" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D37">
     <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D25)))</formula>
     </cfRule>
@@ -2027,76 +2149,76 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32:D37">
+  <conditionalFormatting sqref="D39:D44">
     <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D32)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D39)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D32)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D39:D44">
-    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D39)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46:D51">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D46)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D46)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D53:D58">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D53)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D53)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D60:D65">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D60)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D60)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D67:D72">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D67)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D67)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D74:D79">
-    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D74)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D74)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:D86">
-    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D81)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D81)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D88">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
+  <conditionalFormatting sqref="D88:D93">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D88)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D88)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D95">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D95)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D88)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D95)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2108,8 +2230,8 @@
     <oddFooter>&amp;L&amp;8&amp;F&amp;R&amp;8Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="52" max="16383" man="1"/>
-    <brk id="88" max="3" man="1"/>
+    <brk id="59" max="16383" man="1"/>
+    <brk id="95" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B59FD28-21C8-4444-AEF2-D12B3D4AF60F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1903F389-AE22-4D64-BF2E-26059210A6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -171,7 +171,28 @@
     <t>Installation OS - Problème et solution détaillée au point 6.1.1</t>
   </si>
   <si>
-    <t>Installation Cluster</t>
+    <t>Création des OSD Ceph - Problème et solution au point 6.2.2</t>
+  </si>
+  <si>
+    <t>Configurer le cluster - Problème et solution au point 6.2.1</t>
+  </si>
+  <si>
+    <t>Ajouter les utilisateurs nécessaires</t>
+  </si>
+  <si>
+    <t>Accorder les accès aux utilisateurs</t>
+  </si>
+  <si>
+    <t>Et c'est là ou le fun commence ! J'aime les problèmes !</t>
+  </si>
+  <si>
+    <t>Mettre en place l'infra nécessaire à Ansible (LXC + Codebase)</t>
+  </si>
+  <si>
+    <t>Tester la connexion Ansible - Cluster</t>
+  </si>
+  <si>
+    <t>Sysprep les OS</t>
   </si>
 </sst>
 </file>
@@ -269,7 +290,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -369,17 +390,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
@@ -415,17 +425,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -479,11 +478,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -523,139 +522,139 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -663,29 +662,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1267,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1278,123 +1255,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="37"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
+      <c r="A6" s="30">
         <v>46153</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="21"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="17"/>
-      <c r="B8" s="20" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="21"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="17"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="21"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="17"/>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="21"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="17"/>
-      <c r="B12" s="13" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1407,72 +1384,72 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="17"/>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16">
+      <c r="A16" s="17">
         <v>46154</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="16"/>
       <c r="D16" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="18"/>
+      <c r="B17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="17"/>
-      <c r="B18" s="20" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="21"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="17"/>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="21"/>
+      <c r="C19" s="16"/>
       <c r="D19" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="17"/>
+      <c r="A20" s="18"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="17"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="17"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="17"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1485,97 +1462,97 @@
       </c>
     </row>
     <row r="24" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="17"/>
-      <c r="B24" s="22" t="s">
+      <c r="A24" s="18"/>
+      <c r="B24" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
-    </row>
-    <row r="25" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16">
+      <c r="C24" s="22"/>
+      <c r="D24" s="23"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="17">
         <v>46157</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="21"/>
+      <c r="C25" s="16"/>
       <c r="D25" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="17"/>
-      <c r="B26" s="20" t="s">
+      <c r="A26" s="18"/>
+      <c r="B26" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="21"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="17"/>
-      <c r="B27" s="20" t="s">
+      <c r="A27" s="18"/>
+      <c r="B27" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="21"/>
+      <c r="C27" s="16"/>
       <c r="D27" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="17"/>
-      <c r="B28" s="20" t="s">
+      <c r="A28" s="18"/>
+      <c r="B28" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="21"/>
+      <c r="C28" s="16"/>
       <c r="D28" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="17"/>
-      <c r="B29" s="20" t="s">
+      <c r="A29" s="18"/>
+      <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="21"/>
+      <c r="C29" s="16"/>
       <c r="D29" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="17"/>
-      <c r="B30" s="43" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="44"/>
+      <c r="C30" s="16"/>
       <c r="D30" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="17"/>
-      <c r="B31" s="43" t="s">
+      <c r="A31" s="18"/>
+      <c r="B31" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="44"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="17"/>
-      <c r="B32" s="43" t="s">
+      <c r="A32" s="18"/>
+      <c r="B32" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="44"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="8">
         <v>0.3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="17"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="45" t="s">
         <v>31</v>
       </c>
@@ -1585,29 +1562,29 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="17"/>
-      <c r="B34" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="44"/>
+      <c r="A34" s="18"/>
+      <c r="B34" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="42"/>
       <c r="D34" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="17"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="44"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="8"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="17"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="44"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="20"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="17"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="2" t="s">
         <v>6</v>
       </c>
@@ -1620,424 +1597,550 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="17"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="24"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23"/>
     </row>
     <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="16"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="7"/>
+      <c r="A39" s="17">
+        <v>46160</v>
+      </c>
+      <c r="B39" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="44"/>
+      <c r="D39" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="17"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="8"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="8">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="17"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="8"/>
+      <c r="A41" s="18"/>
+      <c r="B41" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="16"/>
+      <c r="D41" s="8">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="17"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="8"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="17"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="8"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="17"/>
-      <c r="B44" s="2" t="s">
+      <c r="A44" s="18"/>
+      <c r="B44" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="18"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="18"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="8"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="18"/>
+      <c r="B47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D47" s="9">
         <f>SUM(D39:D43)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="27"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="26"/>
+    </row>
+    <row r="49" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="17"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="18"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="8"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="18"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="8"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="18"/>
+      <c r="B52" s="15"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="8"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="18"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="18"/>
+      <c r="B54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="9">
+        <f>SUM(D49:D53)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="25"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="28"/>
-    </row>
-    <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="16"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="7"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="17"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="8"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="17"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="8"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="8"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="17"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="8"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="17"/>
-      <c r="B51" s="2" t="s">
+    <row r="55" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="27"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="26"/>
+    </row>
+    <row r="56" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="17"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="18"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="8"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="18"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="8"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="18"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="8"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="18"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="8"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="18"/>
+      <c r="B61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D51" s="9">
-        <f>SUM(D46:D50)</f>
+      <c r="D61" s="9">
+        <f>SUM(D56:D60)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="25"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="28"/>
-    </row>
-    <row r="53" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="16"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="7"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="17"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="8"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="17"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="8"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="17"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="17"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="21"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="17"/>
-      <c r="B58" s="2" t="s">
+    <row r="62" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="27"/>
+      <c r="B62" s="24"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="26"/>
+    </row>
+    <row r="63" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="17"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="7"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="18"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="8"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="18"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="8"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="18"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="8"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="18"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="8"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="18"/>
+      <c r="B68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D58" s="9">
-        <f>SUM(D53:D57)</f>
+      <c r="D68" s="9">
+        <f>SUM(D63:D67)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="25"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="28"/>
-    </row>
-    <row r="60" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="16"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="7"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="17"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="8"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="17"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="8"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="17"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="21"/>
-      <c r="D63" s="8"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="17"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="8"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="17"/>
-      <c r="B65" s="2" t="s">
+    <row r="69" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="27"/>
+      <c r="B69" s="24"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="26"/>
+    </row>
+    <row r="70" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="17"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="7"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="18"/>
+      <c r="B71" s="15"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="18"/>
+      <c r="B72" s="15"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="18"/>
+      <c r="B73" s="15"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="8"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="18"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="18"/>
+      <c r="B75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D65" s="9">
-        <f>SUM(D60:D64)</f>
+      <c r="D75" s="9">
+        <f>SUM(D70:D74)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="25"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="28"/>
-    </row>
-    <row r="67" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="16"/>
-      <c r="B67" s="18"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="7"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="17"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="8"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="17"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="8"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="17"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="21"/>
-      <c r="D70" s="8"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="17"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="8"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="17"/>
-      <c r="B72" s="2" t="s">
+    <row r="76" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="27"/>
+      <c r="B76" s="24"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="26"/>
+    </row>
+    <row r="77" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="17"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="7"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="18"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="16"/>
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="18"/>
+      <c r="B79" s="15"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="8"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="18"/>
+      <c r="B80" s="15"/>
+      <c r="C80" s="16"/>
+      <c r="D80" s="8"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="18"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="18"/>
+      <c r="B82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D72" s="9">
-        <f>SUM(D67:D71)</f>
+      <c r="D82" s="9">
+        <f>SUM(D77:D81)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="25"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="27"/>
-      <c r="D73" s="28"/>
-    </row>
-    <row r="74" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="16"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="7"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="17"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="8"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="17"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="8"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="17"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="21"/>
-      <c r="D77" s="8"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="17"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="8"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="17"/>
-      <c r="B79" s="2" t="s">
+    <row r="83" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="18"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="22"/>
+      <c r="D83" s="23"/>
+    </row>
+    <row r="84" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="17"/>
+      <c r="B84" s="28"/>
+      <c r="C84" s="29"/>
+      <c r="D84" s="7"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="18"/>
+      <c r="B85" s="15"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="18"/>
+      <c r="B86" s="15"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="18"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="18"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="16"/>
+      <c r="D88" s="8"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="18"/>
+      <c r="B89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D79" s="9">
-        <f>SUM(D74:D78)</f>
+      <c r="D89" s="9">
+        <f>SUM(D84:D88)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="17"/>
-      <c r="B80" s="22"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="24"/>
-    </row>
-    <row r="81" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="16"/>
-      <c r="B81" s="18"/>
-      <c r="C81" s="19"/>
-      <c r="D81" s="7"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="17"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="21"/>
-      <c r="D82" s="8"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="17"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="21"/>
-      <c r="D83" s="8"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="17"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="21"/>
-      <c r="D84" s="8"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="17"/>
-      <c r="B85" s="20"/>
-      <c r="C85" s="21"/>
-      <c r="D85" s="8"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="17"/>
-      <c r="B86" s="2" t="s">
+    <row r="90" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="27"/>
+      <c r="B90" s="24"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="26"/>
+    </row>
+    <row r="91" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="17"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="29"/>
+      <c r="D91" s="7"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="18"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="18"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="8"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="18"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="8"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="18"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="8"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="18"/>
+      <c r="B96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D86" s="9">
-        <f>SUM(D81:D85)</f>
+      <c r="D96" s="9">
+        <f>SUM(D91:D95)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="27"/>
-      <c r="D87" s="28"/>
-    </row>
-    <row r="88" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="16"/>
-      <c r="B88" s="18"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="7"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="17"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="21"/>
-      <c r="D89" s="8"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="17"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="21"/>
-      <c r="D90" s="8"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="17"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="21"/>
-      <c r="D91" s="8"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="17"/>
-      <c r="B92" s="20"/>
-      <c r="C92" s="21"/>
-      <c r="D92" s="8"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="17"/>
-      <c r="B93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="9">
-        <f>SUM(D88:D92)</f>
+    <row r="97" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="27"/>
+      <c r="B97" s="24"/>
+      <c r="C97" s="25"/>
+      <c r="D97" s="26"/>
+    </row>
+    <row r="98" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="11"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" s="12">
+        <f>D14+D23+D37+D47+D54+D61+D68+D75+D82+D89+D96</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="40" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="25"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="27"/>
-      <c r="D94" s="28"/>
-    </row>
-    <row r="95" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="11"/>
-      <c r="B95" s="10"/>
-      <c r="C95" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="12">
-        <f>D14+D23+D37+D44+D51+D58+D65+D72+D79+D86+D93</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B96" s="15"/>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
+      <c r="B99" s="40"/>
+      <c r="C99" s="40"/>
+      <c r="D99" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="96">
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A39:A48"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="A77:A83"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A63:A69"/>
+    <mergeCell ref="A84:A90"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="A91:A97"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B97:D97"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B76:D76"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="A25:A38"/>
@@ -2051,174 +2154,88 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B94:D94"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A96:D96"/>
-    <mergeCell ref="A16:A24"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="A46:A52"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D14 D16:D19 D21:D23 D25">
-    <cfRule type="containsText" dxfId="21" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25 D6:D14 D16:D19 D21:D23">
-    <cfRule type="containsText" dxfId="20" priority="23" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25:D37">
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="Terminé">
+  <conditionalFormatting sqref="D25:D37 D39:D47">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D25)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D39:D44">
-    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D39)))</formula>
+  <conditionalFormatting sqref="D49:D54">
+    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D49)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D39)))</formula>
+    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D49)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D46:D51">
-    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D46)))</formula>
+  <conditionalFormatting sqref="D56:D61">
+    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D56)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D46)))</formula>
+    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D56)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D53:D58">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D53)))</formula>
+  <conditionalFormatting sqref="D63:D68">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D53)))</formula>
+    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D63)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D60:D65">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D60)))</formula>
+  <conditionalFormatting sqref="D70:D75">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D70)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D60)))</formula>
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D70)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D67:D72">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D67)))</formula>
+  <conditionalFormatting sqref="D77:D82">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D77)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D67)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D77)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D74:D79">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D74)))</formula>
+  <conditionalFormatting sqref="D84:D89">
+    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D84)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D74)))</formula>
+    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D84)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D81:D86">
-    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D81)))</formula>
+  <conditionalFormatting sqref="D91:D96">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D91)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D81)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D91)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D88:D93">
-    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D88)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D88)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D95">
+  <conditionalFormatting sqref="D98">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D95)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D98)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D95)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D98)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2230,8 +2247,8 @@
     <oddFooter>&amp;L&amp;8&amp;F&amp;R&amp;8Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="59" max="16383" man="1"/>
-    <brk id="95" max="3" man="1"/>
+    <brk id="62" max="16383" man="1"/>
+    <brk id="98" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1903F389-AE22-4D64-BF2E-26059210A6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FA3DEA-F154-4E34-ACD1-D5DBE779A33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$101</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -183,9 +183,6 @@
     <t>Accorder les accès aux utilisateurs</t>
   </si>
   <si>
-    <t>Et c'est là ou le fun commence ! J'aime les problèmes !</t>
-  </si>
-  <si>
     <t>Mettre en place l'infra nécessaire à Ansible (LXC + Codebase)</t>
   </si>
   <si>
@@ -193,6 +190,20 @@
   </si>
   <si>
     <t>Sysprep les OS</t>
+  </si>
+  <si>
+    <t>Je n'ai pas grand-chose à raconter outre que ça avance beaucoup plus vite qu'anticipé. Je me sousestime grandement il semblerait. Je pense que ça vient du fait que je n'ai pas beaucoup eu d'occasion de tester mes capacités en situation réelles, les projets de modules étant habituellements centrés sur une ou deux compétences.</t>
+  </si>
+  <si>
+    <t>Et c'est là ou le fun commence ! J'aime les problèmes ! Tant que je ne casse pas quelque chose de critique… Mais même là, le cluster fait que je réplique tout sur 3 machines, c'est largement récupérable.</t>
+  </si>
+  <si>
+    <t>J'ai posé la question suivante lors de la préparation de la machine: "Bonjour,
+Je suis en train de Sysprep le server windows, est-ce qu'il y a des programmes spécifiques voulus par l'EMF ? Ou alors un fond d'écran personnalisé ? Ou alors des documents qui devraient être présents, comme les bonnes pratiques ou autre ?
+Le cahier des charges ne spécifie rien de particulier, seulement que la VM doit être aux standards prédéfinis. J'ai donc déjà suivi les standards d'entreprise."</t>
+  </si>
+  <si>
+    <t>Créer Template</t>
   </si>
 </sst>
 </file>
@@ -473,7 +484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -522,6 +533,126 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -531,22 +662,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -554,108 +669,20 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1244,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1293,949 +1320,988 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="30">
+      <c r="A6" s="40">
         <v>46153</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="15" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="18"/>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="16"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="18"/>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="15" t="s">
+      <c r="A11" s="21"/>
+      <c r="B11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="21"/>
+      <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="18"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="32"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="18"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="21"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="21"/>
+      <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="9">
-        <f>SUM(D6:D13)</f>
+      <c r="D15" s="9">
+        <f>SUM(D6:D14)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="21" t="s">
+    <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="21"/>
+      <c r="B16" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-    </row>
-    <row r="16" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="17">
+      <c r="C16" s="23"/>
+      <c r="D16" s="24"/>
+    </row>
+    <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="20">
         <v>46154</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="7">
+      <c r="C17" s="18"/>
+      <c r="D17" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="18"/>
-      <c r="B17" s="15" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="21"/>
+      <c r="B18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="8">
+      <c r="C18" s="18"/>
+      <c r="D18" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="18"/>
-      <c r="B18" s="15" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="21"/>
+      <c r="B19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="8">
+      <c r="C19" s="18"/>
+      <c r="D19" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="15" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="21"/>
+      <c r="B20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="8">
+      <c r="C20" s="18"/>
+      <c r="D20" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-    </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="18"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="8"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="16"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="21"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="21"/>
+      <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="9">
-        <f>SUM(D16:D22)</f>
+      <c r="D24" s="9">
+        <f>SUM(D17:D23)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="21" t="s">
+    <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21"/>
+      <c r="B25" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="23"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="17">
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="20">
         <v>46157</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B26" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="8">
+      <c r="C26" s="18"/>
+      <c r="D26" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="15" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="21"/>
+      <c r="B27" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="8">
+      <c r="C27" s="18"/>
+      <c r="D27" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="15" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="21"/>
+      <c r="B28" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="16"/>
-      <c r="D27" s="8">
+      <c r="C28" s="18"/>
+      <c r="D28" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="15" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="21"/>
+      <c r="B29" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="8">
+      <c r="C29" s="18"/>
+      <c r="D29" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="18"/>
-      <c r="B29" s="15" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="21"/>
+      <c r="B30" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="8">
+      <c r="C30" s="18"/>
+      <c r="D30" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="18"/>
-      <c r="B30" s="15" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="21"/>
+      <c r="B31" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="18"/>
       <c r="D31" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="B32" s="15" t="s">
+      <c r="A32" s="21"/>
+      <c r="B32" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="21"/>
+      <c r="B33" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="8">
+      <c r="C33" s="18"/>
+      <c r="D33" s="8">
         <v>0.3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="18"/>
-      <c r="B33" s="45" t="s">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="21"/>
+      <c r="B34" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="46"/>
-      <c r="D33" s="8">
+      <c r="C34" s="48"/>
+      <c r="D34" s="8">
         <v>0.7</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="18"/>
-      <c r="B34" s="41" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="21"/>
+      <c r="B35" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="8">
+      <c r="C35" s="27"/>
+      <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="8"/>
-    </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="20"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="14"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="18"/>
-      <c r="B37" s="2" t="s">
+      <c r="A37" s="21"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="8"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="21"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="8"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="21"/>
+      <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D37" s="9">
-        <f>SUM(D25:D36)</f>
+      <c r="D39" s="9">
+        <f>SUM(D26:D38)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="18"/>
-      <c r="B38" s="21" t="s">
+    <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="21"/>
+      <c r="B40" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="23"/>
+      <c r="D40" s="24"/>
+    </row>
+    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="20">
+        <v>46160</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="29"/>
+      <c r="D41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="21"/>
+      <c r="B42" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="21"/>
+      <c r="B43" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="21"/>
+      <c r="B44" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="23"/>
-    </row>
-    <row r="39" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="17">
-        <v>46160</v>
-      </c>
-      <c r="B39" s="43" t="s">
+      <c r="C44" s="18"/>
+      <c r="D44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="21"/>
+      <c r="B45" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="18"/>
+      <c r="D45" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="21"/>
+      <c r="B46" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="18"/>
+      <c r="D46" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="21"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="8"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="21"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="8"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="21"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="8"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="21"/>
+      <c r="B50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="9">
+        <f>SUM(D41:D46)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="25"/>
+      <c r="B51" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="31"/>
+      <c r="D51" s="32"/>
+    </row>
+    <row r="52" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="20">
+        <v>46161</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="18"/>
+      <c r="D52" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="21"/>
+      <c r="B53" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="18"/>
+      <c r="D53" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="21"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="21"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="21"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="8"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="21"/>
+      <c r="B57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="9">
+        <f>SUM(D52:D56)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="25"/>
+      <c r="B58" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="31"/>
+      <c r="D58" s="32"/>
+    </row>
+    <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="20"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="21"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="8"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="21"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="21"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="21"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="8"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="21"/>
+      <c r="B64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="9">
+        <f>SUM(D59:D63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="25"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="32"/>
+    </row>
+    <row r="66" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="20"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="21"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="8"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="21"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="8"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="21"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="8"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="21"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="8"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="21"/>
+      <c r="B71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="9">
+        <f>SUM(D66:D70)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="25"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="32"/>
+    </row>
+    <row r="73" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="20"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="7"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="21"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="8"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="21"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="8"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="21"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="21"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="21"/>
+      <c r="B78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="9">
+        <f>SUM(D73:D77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="25"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="32"/>
+    </row>
+    <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="20"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="7"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="21"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="8"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="21"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="8"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="21"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="21"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="21"/>
+      <c r="B85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="9">
+        <f>SUM(D80:D84)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="21"/>
+      <c r="B86" s="22"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="24"/>
+    </row>
+    <row r="87" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="20"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="42"/>
+      <c r="D87" s="7"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="21"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="8"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="21"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="18"/>
+      <c r="D89" s="8"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="21"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="18"/>
+      <c r="D90" s="8"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="21"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="18"/>
+      <c r="D91" s="8"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="21"/>
+      <c r="B92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="9">
+        <f>SUM(D87:D91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="25"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="31"/>
+      <c r="D93" s="32"/>
+    </row>
+    <row r="94" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="20"/>
+      <c r="B94" s="41"/>
+      <c r="C94" s="42"/>
+      <c r="D94" s="7"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="21"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="18"/>
+      <c r="D95" s="8"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="21"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="18"/>
+      <c r="D96" s="8"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="21"/>
+      <c r="B97" s="17"/>
+      <c r="C97" s="18"/>
+      <c r="D97" s="8"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="21"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="18"/>
+      <c r="D98" s="8"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="21"/>
+      <c r="B99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="9">
+        <f>SUM(D94:D98)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="25"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="31"/>
+      <c r="D100" s="32"/>
+    </row>
+    <row r="101" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="11"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="12">
+        <f>D15+D24+D39+D50+D57+D64+D71+D78+D85+D92+D99</f>
         <v>32</v>
       </c>
-      <c r="C39" s="44"/>
-      <c r="D39" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="18"/>
-      <c r="B41" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="18"/>
-      <c r="B42" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
-      <c r="B44" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="8"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="18"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="8"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="18"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="8"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="9">
-        <f>SUM(D39:D43)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="27"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="26"/>
-    </row>
-    <row r="49" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="17"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="7"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="18"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="8"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="18"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="8"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="18"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="8"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="18"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="8"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="18"/>
-      <c r="B54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="9">
-        <f>SUM(D49:D53)</f>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="19" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="27"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="26"/>
-    </row>
-    <row r="56" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="17"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="29"/>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="18"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="18"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="8"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="18"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="8"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="18"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="8"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="18"/>
-      <c r="B61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="9">
-        <f>SUM(D56:D60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="27"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="26"/>
-    </row>
-    <row r="63" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="17"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="7"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="18"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="8"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="18"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="8"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="18"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="8"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="18"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="8"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="18"/>
-      <c r="B68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="9">
-        <f>SUM(D63:D67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="27"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="26"/>
-    </row>
-    <row r="70" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="17"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="7"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="18"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="8"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="18"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="8"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="18"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="8"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="18"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="8"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="18"/>
-      <c r="B75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="9">
-        <f>SUM(D70:D74)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="27"/>
-      <c r="B76" s="24"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="26"/>
-    </row>
-    <row r="77" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="17"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="7"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="18"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="8"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="18"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="8"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="18"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="8"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="18"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="8"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="18"/>
-      <c r="B82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="9">
-        <f>SUM(D77:D81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="18"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="23"/>
-    </row>
-    <row r="84" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="17"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="29"/>
-      <c r="D84" s="7"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="18"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="8"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="18"/>
-      <c r="B86" s="15"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="8"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="18"/>
-      <c r="B87" s="15"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="8"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="18"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="8"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="18"/>
-      <c r="B89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D89" s="9">
-        <f>SUM(D84:D88)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="27"/>
-      <c r="B90" s="24"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="26"/>
-    </row>
-    <row r="91" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="17"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="7"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="18"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="16"/>
-      <c r="D92" s="8"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="18"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="16"/>
-      <c r="D93" s="8"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="18"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="16"/>
-      <c r="D94" s="8"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="18"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="8"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="18"/>
-      <c r="B96" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="9">
-        <f>SUM(D91:D95)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="27"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="26"/>
-    </row>
-    <row r="98" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="11"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="12">
-        <f>D14+D23+D37+D47+D54+D61+D68+D75+D82+D89+D96</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" s="40"/>
-      <c r="C99" s="40"/>
-      <c r="D99" s="40"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A16:A24"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A39:A48"/>
+  <mergeCells count="99">
+    <mergeCell ref="A26:A40"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A94:A100"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="A80:A86"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="A59:A65"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="A66:A72"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A52:A58"/>
     <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="A77:A83"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="A63:A69"/>
-    <mergeCell ref="A84:A90"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B90:D90"/>
-    <mergeCell ref="A91:A97"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B97:D97"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="A70:A76"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="A25:A38"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B47:C47"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D14 D16:D19 D21:D23 D25">
+  <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
     <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25 D6:D14 D16:D19 D21:D23">
+  <conditionalFormatting sqref="D26 D6:D15 D17:D20 D22:D24">
     <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25:D37 D39:D47">
+  <conditionalFormatting sqref="D26:D39 D41:D50">
     <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D25)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D26)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D25)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D26)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D49:D54">
+  <conditionalFormatting sqref="D52:D57">
     <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D49)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D52)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D49)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D52)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D56:D61">
+  <conditionalFormatting sqref="D59:D64">
     <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D56)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D59)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D56)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D59)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D63:D68">
+  <conditionalFormatting sqref="D66:D71">
     <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D63)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D66)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D63)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D66)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D70:D75">
+  <conditionalFormatting sqref="D73:D78">
     <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D70)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D73)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D70)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D73)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D77:D82">
+  <conditionalFormatting sqref="D80:D85">
     <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D77)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D80)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D77)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D80)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D84:D89">
+  <conditionalFormatting sqref="D87:D92">
     <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D84)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D87)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D84)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D87)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D91:D96">
+  <conditionalFormatting sqref="D94:D99">
     <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D91)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D94)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D91)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D94)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D98">
+  <conditionalFormatting sqref="D101">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D98)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D101)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D98)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D101)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2247,8 +2313,8 @@
     <oddFooter>&amp;L&amp;8&amp;F&amp;R&amp;8Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="62" max="16383" man="1"/>
-    <brk id="98" max="3" man="1"/>
+    <brk id="65" max="16383" man="1"/>
+    <brk id="101" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FA3DEA-F154-4E34-ACD1-D5DBE779A33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27647D7A-972C-4EF1-8A37-5718DC958C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -205,6 +205,43 @@
   <si>
     <t>Créer Template</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Playbook qui reçoit un 403: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF92D050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Problème et solution au point 6.2.4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Playbook ne trouve pas le template: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF92D050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Problème et solution au point 6.2.3</t>
+    </r>
+  </si>
+  <si>
+    <t>J'ai passé 2h sur une erreur d'orthographe T-T Vraiment je me fatigue</t>
+  </si>
+  <si>
+    <t>Créer le playbook pour créer les VMs</t>
+  </si>
+  <si>
+    <t>Créer le playbook pour détruire les VMs</t>
+  </si>
 </sst>
 </file>
 
@@ -214,7 +251,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -280,6 +317,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF92D050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -484,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -533,6 +576,74 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -542,66 +653,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -654,14 +705,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -675,21 +718,57 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1282,129 +1361,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="35"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40">
+      <c r="A6" s="42">
         <v>46153</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="18"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="21"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="21"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="23"/>
+      <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="18"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="21"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="23"/>
+      <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="16"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="21"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="18"/>
+      <c r="C11" s="16"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="18"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="18"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="21"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1417,74 +1496,74 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20">
+      <c r="A17" s="22">
         <v>46154</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="18"/>
+      <c r="C17" s="16"/>
       <c r="D17" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="17" t="s">
+      <c r="A18" s="23"/>
+      <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="18"/>
+      <c r="C18" s="16"/>
       <c r="D18" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="21"/>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="23"/>
+      <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="18"/>
+      <c r="C19" s="16"/>
       <c r="D19" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="21"/>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="18"/>
+      <c r="C20" s="16"/>
       <c r="D20" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="21"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="44"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="21"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="16"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1497,97 +1576,97 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="20">
+      <c r="A26" s="22">
         <v>46157</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="18"/>
+      <c r="C26" s="16"/>
       <c r="D26" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="21"/>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="18"/>
+      <c r="C27" s="16"/>
       <c r="D27" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
-      <c r="B28" s="17" t="s">
+      <c r="A28" s="23"/>
+      <c r="B28" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="18"/>
+      <c r="C28" s="16"/>
       <c r="D28" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
-      <c r="B29" s="17" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="18"/>
+      <c r="C29" s="16"/>
       <c r="D29" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
-      <c r="B30" s="17" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="18"/>
+      <c r="C30" s="16"/>
       <c r="D30" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="21"/>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="23"/>
+      <c r="B31" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="18"/>
+      <c r="C31" s="16"/>
       <c r="D31" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="21"/>
-      <c r="B32" s="17" t="s">
+      <c r="A32" s="23"/>
+      <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="18"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="21"/>
-      <c r="B33" s="17" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="18"/>
+      <c r="C33" s="16"/>
       <c r="D33" s="8">
         <v>0.3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="21"/>
+      <c r="A34" s="23"/>
       <c r="B34" s="47" t="s">
         <v>31</v>
       </c>
@@ -1597,35 +1676,35 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="21"/>
-      <c r="B35" s="26" t="s">
+      <c r="A35" s="23"/>
+      <c r="B35" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="27"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="21"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="14"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="21"/>
+      <c r="A37" s="23"/>
       <c r="B37" s="45"/>
       <c r="C37" s="46"/>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
+      <c r="A38" s="23"/>
       <c r="B38" s="45"/>
       <c r="C38" s="46"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="21"/>
+      <c r="A39" s="23"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1638,95 +1717,95 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21"/>
-      <c r="B40" s="22" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="23"/>
-      <c r="D40" s="24"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="26"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="20">
+      <c r="A41" s="22">
         <v>46160</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="29"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="17" t="s">
+      <c r="A42" s="23"/>
+      <c r="B42" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="18"/>
+      <c r="C42" s="16"/>
       <c r="D42" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="21"/>
-      <c r="B43" s="17" t="s">
+      <c r="A43" s="23"/>
+      <c r="B43" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="18"/>
+      <c r="C43" s="16"/>
       <c r="D43" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="21"/>
-      <c r="B44" s="17" t="s">
+      <c r="A44" s="23"/>
+      <c r="B44" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="18"/>
+      <c r="C44" s="16"/>
       <c r="D44" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="21"/>
-      <c r="B45" s="17" t="s">
+      <c r="A45" s="23"/>
+      <c r="B45" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="18"/>
+      <c r="C45" s="16"/>
       <c r="D45" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
-      <c r="B46" s="17" t="s">
+      <c r="A46" s="23"/>
+      <c r="B46" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="18"/>
+      <c r="C46" s="16"/>
       <c r="D46" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="21"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="16"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="21"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="16"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="21"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="16"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="21"/>
+      <c r="A50" s="23"/>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1739,55 +1818,59 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="25"/>
-      <c r="B51" s="30" t="s">
+      <c r="A51" s="27"/>
+      <c r="B51" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="31"/>
-      <c r="D51" s="32"/>
-    </row>
-    <row r="52" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="20">
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
+    </row>
+    <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="22">
         <v>46161</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="18"/>
+      <c r="C52" s="16"/>
       <c r="D52" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="21"/>
-      <c r="B53" s="17" t="s">
+      <c r="A53" s="23"/>
+      <c r="B53" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="18"/>
+      <c r="C53" s="16"/>
       <c r="D53" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="21"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="8"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="16"/>
+      <c r="D54" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="21"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="16"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="21"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="18"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="16"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="21"/>
+      <c r="A57" s="23"/>
       <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1800,45 +1883,59 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="25"/>
-      <c r="B58" s="30" t="s">
+      <c r="A58" s="27"/>
+      <c r="B58" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="31"/>
-      <c r="D58" s="32"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
-      <c r="B59" s="41"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="7"/>
+      <c r="A59" s="22">
+        <v>46163</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" s="29"/>
+      <c r="D59" s="7">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="21"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="8"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" s="29"/>
+      <c r="D60" s="8">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="8"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="16"/>
+      <c r="D61" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="21"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="16"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="21"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="18"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="15"/>
+      <c r="C63" s="16"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="21"/>
+      <c r="A64" s="23"/>
       <c r="B64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1847,47 +1944,49 @@
       </c>
       <c r="D64" s="9">
         <f>SUM(D59:D63)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="25"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="32"/>
-    </row>
-    <row r="66" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="20"/>
-      <c r="B66" s="41"/>
-      <c r="C66" s="42"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="22"/>
+      <c r="B66" s="43"/>
+      <c r="C66" s="44"/>
       <c r="D66" s="7"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="21"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="16"/>
       <c r="D67" s="8"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="21"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="18"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="15"/>
+      <c r="C68" s="16"/>
       <c r="D68" s="8"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="21"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="16"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="21"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="14"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="21"/>
+      <c r="A71" s="23"/>
       <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
@@ -1900,43 +1999,43 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="25"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="31"/>
-      <c r="D72" s="32"/>
-    </row>
-    <row r="73" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="20"/>
-      <c r="B73" s="41"/>
-      <c r="C73" s="42"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="34"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="22"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
       <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="21"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="18"/>
+      <c r="A74" s="23"/>
+      <c r="B74" s="15"/>
+      <c r="C74" s="16"/>
       <c r="D74" s="8"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="21"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="18"/>
+      <c r="A75" s="23"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="16"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="21"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
+      <c r="A76" s="23"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="16"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="21"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="18"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="21"/>
+      <c r="A78" s="23"/>
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
@@ -1949,43 +2048,43 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="25"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="32"/>
+      <c r="A79" s="27"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="34"/>
     </row>
     <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="20"/>
-      <c r="B80" s="41"/>
-      <c r="C80" s="42"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="44"/>
       <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="21"/>
-      <c r="B81" s="17"/>
-      <c r="C81" s="18"/>
+      <c r="A81" s="23"/>
+      <c r="B81" s="15"/>
+      <c r="C81" s="16"/>
       <c r="D81" s="8"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="21"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="18"/>
+      <c r="A82" s="23"/>
+      <c r="B82" s="15"/>
+      <c r="C82" s="16"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="21"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="18"/>
+      <c r="A83" s="23"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="16"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="21"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="18"/>
+      <c r="A84" s="23"/>
+      <c r="B84" s="15"/>
+      <c r="C84" s="16"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="21"/>
+      <c r="A85" s="23"/>
       <c r="B85" s="2" t="s">
         <v>6</v>
       </c>
@@ -1998,43 +2097,43 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="21"/>
-      <c r="B86" s="22"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="24"/>
+      <c r="A86" s="23"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="26"/>
     </row>
     <row r="87" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="20"/>
-      <c r="B87" s="41"/>
-      <c r="C87" s="42"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="44"/>
       <c r="D87" s="7"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="21"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="18"/>
+      <c r="A88" s="23"/>
+      <c r="B88" s="15"/>
+      <c r="C88" s="16"/>
       <c r="D88" s="8"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="21"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="18"/>
+      <c r="A89" s="23"/>
+      <c r="B89" s="15"/>
+      <c r="C89" s="16"/>
       <c r="D89" s="8"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="21"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="18"/>
+      <c r="A90" s="23"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="16"/>
       <c r="D90" s="8"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="21"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="18"/>
+      <c r="A91" s="23"/>
+      <c r="B91" s="15"/>
+      <c r="C91" s="16"/>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="21"/>
+      <c r="A92" s="23"/>
       <c r="B92" s="2" t="s">
         <v>6</v>
       </c>
@@ -2047,43 +2146,43 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="25"/>
-      <c r="B93" s="30"/>
-      <c r="C93" s="31"/>
-      <c r="D93" s="32"/>
+      <c r="A93" s="27"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="34"/>
     </row>
     <row r="94" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="20"/>
-      <c r="B94" s="41"/>
-      <c r="C94" s="42"/>
+      <c r="A94" s="22"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="44"/>
       <c r="D94" s="7"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="21"/>
-      <c r="B95" s="17"/>
-      <c r="C95" s="18"/>
+      <c r="A95" s="23"/>
+      <c r="B95" s="15"/>
+      <c r="C95" s="16"/>
       <c r="D95" s="8"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="21"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="18"/>
+      <c r="A96" s="23"/>
+      <c r="B96" s="15"/>
+      <c r="C96" s="16"/>
       <c r="D96" s="8"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="21"/>
-      <c r="B97" s="17"/>
-      <c r="C97" s="18"/>
+      <c r="A97" s="23"/>
+      <c r="B97" s="15"/>
+      <c r="C97" s="16"/>
       <c r="D97" s="8"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="21"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="18"/>
+      <c r="A98" s="23"/>
+      <c r="B98" s="15"/>
+      <c r="C98" s="16"/>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="21"/>
+      <c r="A99" s="23"/>
       <c r="B99" s="2" t="s">
         <v>6</v>
       </c>
@@ -2096,10 +2195,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="25"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="31"/>
-      <c r="D100" s="32"/>
+      <c r="A100" s="27"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="34"/>
     </row>
     <row r="101" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="11"/>
@@ -2109,19 +2208,19 @@
       </c>
       <c r="D101" s="12">
         <f>D15+D24+D39+D50+D57+D64+D71+D78+D85+D92+D99</f>
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="19" t="s">
+      <c r="A102" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="19"/>
+      <c r="B102" s="21"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="99">
+  <mergeCells count="100">
     <mergeCell ref="A26:A40"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
@@ -2134,6 +2233,7 @@
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="A73:A79"/>
     <mergeCell ref="B73:C73"/>
@@ -2223,84 +2323,84 @@
     <mergeCell ref="B47:C47"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
-    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="23" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26 D6:D15 D17:D20 D22:D24">
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26:D39 D41:D50">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52:D57">
-    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D52)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D64">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D59)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66:D71">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D66)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73:D78">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D73)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D73)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D80:D85">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D80)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="10" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D80)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:D92">
-    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D87)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D87)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D94:D99">
-    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D94)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D94)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D101)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D101)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27647D7A-972C-4EF1-8A37-5718DC958C5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED819A8-5EE4-4FDA-9FC8-59367FEA6138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -241,6 +241,15 @@
   </si>
   <si>
     <t>Créer le playbook pour détruire les VMs</t>
+  </si>
+  <si>
+    <t>Finir le debug du playbook de création de VMs</t>
+  </si>
+  <si>
+    <t>Créer le playbook pour supprimmer des VMs</t>
+  </si>
+  <si>
+    <t>Recréer un sysprep de windows server: Problème et solution au point 6.2.5</t>
   </si>
 </sst>
 </file>
@@ -576,6 +585,82 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -584,12 +669,48 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -606,169 +727,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1361,45 +1326,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="37"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42">
+      <c r="A6" s="36">
         <v>46153</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -1411,7 +1376,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
+      <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
@@ -1421,7 +1386,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
@@ -1431,7 +1396,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
@@ -1441,7 +1406,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
+      <c r="A10" s="14"/>
       <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
@@ -1451,7 +1416,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
@@ -1461,7 +1426,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
@@ -1471,19 +1436,19 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1496,15 +1461,15 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22">
+      <c r="A17" s="13">
         <v>46154</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -1516,7 +1481,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
+      <c r="A18" s="14"/>
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
@@ -1526,7 +1491,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
@@ -1536,7 +1501,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
         <v>21</v>
       </c>
@@ -1546,24 +1511,24 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1576,15 +1541,15 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
+      <c r="A26" s="13">
         <v>46157</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -1596,7 +1561,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
+      <c r="A27" s="14"/>
       <c r="B27" s="15" t="s">
         <v>24</v>
       </c>
@@ -1606,7 +1571,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
+      <c r="A28" s="14"/>
       <c r="B28" s="15" t="s">
         <v>25</v>
       </c>
@@ -1616,7 +1581,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
+      <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>26</v>
       </c>
@@ -1626,7 +1591,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
+      <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>28</v>
       </c>
@@ -1636,7 +1601,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
+      <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>27</v>
       </c>
@@ -1646,7 +1611,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
+      <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
@@ -1656,7 +1621,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="14"/>
       <c r="B33" s="15" t="s">
         <v>30</v>
       </c>
@@ -1666,45 +1631,45 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
-      <c r="B34" s="47" t="s">
+      <c r="A34" s="14"/>
+      <c r="B34" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="48"/>
+      <c r="C34" s="23"/>
       <c r="D34" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
-      <c r="B35" s="28" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="29"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="31"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
+      <c r="A39" s="14"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1717,27 +1682,27 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="26"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22">
+      <c r="A41" s="13">
         <v>46160</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="31"/>
+      <c r="C41" s="25"/>
       <c r="D41" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
+      <c r="A42" s="14"/>
       <c r="B42" s="15" t="s">
         <v>34</v>
       </c>
@@ -1747,7 +1712,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
+      <c r="A43" s="14"/>
       <c r="B43" s="15" t="s">
         <v>35</v>
       </c>
@@ -1757,7 +1722,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
+      <c r="A44" s="14"/>
       <c r="B44" s="15" t="s">
         <v>36</v>
       </c>
@@ -1767,7 +1732,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="15" t="s">
         <v>37</v>
       </c>
@@ -1777,7 +1742,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
+      <c r="A46" s="14"/>
       <c r="B46" s="15" t="s">
         <v>38</v>
       </c>
@@ -1787,25 +1752,25 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
+      <c r="A47" s="14"/>
       <c r="B47" s="15"/>
       <c r="C47" s="16"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="23"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="15"/>
       <c r="C48" s="16"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="23"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="33"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="23"/>
+      <c r="A50" s="14"/>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1818,15 +1783,15 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="27"/>
-      <c r="B51" s="32" t="s">
+      <c r="A51" s="29"/>
+      <c r="B51" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="34"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="28"/>
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="22">
+      <c r="A52" s="13">
         <v>46161</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -1838,7 +1803,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="23"/>
+      <c r="A53" s="14"/>
       <c r="B53" s="15" t="s">
         <v>42</v>
       </c>
@@ -1848,7 +1813,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="23"/>
+      <c r="A54" s="14"/>
       <c r="B54" s="15" t="s">
         <v>46</v>
       </c>
@@ -1858,19 +1823,19 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="23"/>
+      <c r="A55" s="14"/>
       <c r="B55" s="15"/>
       <c r="C55" s="16"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="23"/>
+      <c r="A56" s="14"/>
       <c r="B56" s="15"/>
       <c r="C56" s="16"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="23"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1883,37 +1848,37 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="32" t="s">
+      <c r="A58" s="29"/>
+      <c r="B58" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="34"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="28"/>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22">
+      <c r="A59" s="13">
         <v>46163</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="29"/>
+      <c r="C59" s="35"/>
       <c r="D59" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="23"/>
-      <c r="B60" s="28" t="s">
+      <c r="A60" s="14"/>
+      <c r="B60" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="29"/>
+      <c r="C60" s="35"/>
       <c r="D60" s="8">
         <v>1.9</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
+      <c r="A61" s="14"/>
       <c r="B61" s="15" t="s">
         <v>47</v>
       </c>
@@ -1923,19 +1888,19 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
+      <c r="A62" s="14"/>
       <c r="B62" s="15"/>
       <c r="C62" s="16"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="23"/>
+      <c r="A63" s="14"/>
       <c r="B63" s="15"/>
       <c r="C63" s="16"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
+      <c r="A64" s="14"/>
       <c r="B64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1948,45 +1913,59 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="27"/>
-      <c r="B65" s="32" t="s">
+      <c r="A65" s="29"/>
+      <c r="B65" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="33"/>
-      <c r="D65" s="34"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="28"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="22"/>
-      <c r="B66" s="43"/>
-      <c r="C66" s="44"/>
-      <c r="D66" s="7"/>
+      <c r="A66" s="13">
+        <v>46164</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="31"/>
+      <c r="D66" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
-      <c r="B67" s="15"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="15" t="s">
+        <v>49</v>
+      </c>
       <c r="C67" s="16"/>
-      <c r="D67" s="8"/>
+      <c r="D67" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="23"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="8"/>
+      <c r="A68" s="14"/>
+      <c r="B68" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="25"/>
+      <c r="D68" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="14"/>
       <c r="B69" s="15"/>
       <c r="C69" s="16"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="23"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="14"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="33"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="23"/>
+      <c r="A71" s="14"/>
       <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
@@ -1995,47 +1974,47 @@
       </c>
       <c r="D71" s="9">
         <f>SUM(D66:D70)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="27"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="34"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="28"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="22"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="44"/>
+      <c r="A73" s="13"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="31"/>
       <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="23"/>
+      <c r="A74" s="14"/>
       <c r="B74" s="15"/>
       <c r="C74" s="16"/>
       <c r="D74" s="8"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
+      <c r="A75" s="14"/>
       <c r="B75" s="15"/>
       <c r="C75" s="16"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="23"/>
+      <c r="A76" s="14"/>
       <c r="B76" s="15"/>
       <c r="C76" s="16"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="23"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="14"/>
+      <c r="A77" s="14"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="33"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="23"/>
+      <c r="A78" s="14"/>
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
@@ -2048,43 +2027,43 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="27"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="34"/>
+      <c r="A79" s="29"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="28"/>
     </row>
     <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="22"/>
-      <c r="B80" s="43"/>
-      <c r="C80" s="44"/>
+      <c r="A80" s="13"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="31"/>
       <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="23"/>
+      <c r="A81" s="14"/>
       <c r="B81" s="15"/>
       <c r="C81" s="16"/>
       <c r="D81" s="8"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="23"/>
+      <c r="A82" s="14"/>
       <c r="B82" s="15"/>
       <c r="C82" s="16"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="23"/>
+      <c r="A83" s="14"/>
       <c r="B83" s="15"/>
       <c r="C83" s="16"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="23"/>
+      <c r="A84" s="14"/>
       <c r="B84" s="15"/>
       <c r="C84" s="16"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="23"/>
+      <c r="A85" s="14"/>
       <c r="B85" s="2" t="s">
         <v>6</v>
       </c>
@@ -2097,43 +2076,43 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="23"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="26"/>
+      <c r="A86" s="14"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="21"/>
     </row>
     <row r="87" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="22"/>
-      <c r="B87" s="43"/>
-      <c r="C87" s="44"/>
+      <c r="A87" s="13"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="31"/>
       <c r="D87" s="7"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="23"/>
+      <c r="A88" s="14"/>
       <c r="B88" s="15"/>
       <c r="C88" s="16"/>
       <c r="D88" s="8"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="23"/>
+      <c r="A89" s="14"/>
       <c r="B89" s="15"/>
       <c r="C89" s="16"/>
       <c r="D89" s="8"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="23"/>
+      <c r="A90" s="14"/>
       <c r="B90" s="15"/>
       <c r="C90" s="16"/>
       <c r="D90" s="8"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="23"/>
+      <c r="A91" s="14"/>
       <c r="B91" s="15"/>
       <c r="C91" s="16"/>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="23"/>
+      <c r="A92" s="14"/>
       <c r="B92" s="2" t="s">
         <v>6</v>
       </c>
@@ -2146,43 +2125,43 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="27"/>
-      <c r="B93" s="32"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="34"/>
+      <c r="A93" s="29"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="28"/>
     </row>
     <row r="94" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="22"/>
-      <c r="B94" s="43"/>
-      <c r="C94" s="44"/>
+      <c r="A94" s="13"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="31"/>
       <c r="D94" s="7"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="23"/>
+      <c r="A95" s="14"/>
       <c r="B95" s="15"/>
       <c r="C95" s="16"/>
       <c r="D95" s="8"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="23"/>
+      <c r="A96" s="14"/>
       <c r="B96" s="15"/>
       <c r="C96" s="16"/>
       <c r="D96" s="8"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="23"/>
+      <c r="A97" s="14"/>
       <c r="B97" s="15"/>
       <c r="C97" s="16"/>
       <c r="D97" s="8"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="23"/>
+      <c r="A98" s="14"/>
       <c r="B98" s="15"/>
       <c r="C98" s="16"/>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="23"/>
+      <c r="A99" s="14"/>
       <c r="B99" s="2" t="s">
         <v>6</v>
       </c>
@@ -2195,10 +2174,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="27"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="34"/>
+      <c r="A100" s="29"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="27"/>
+      <c r="D100" s="28"/>
     </row>
     <row r="101" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="11"/>
@@ -2208,59 +2187,63 @@
       </c>
       <c r="D101" s="12">
         <f>D15+D24+D39+D50+D57+D64+D71+D78+D85+D92+D99</f>
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="21" t="s">
+      <c r="A102" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B102" s="21"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A26:A40"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A94:A100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="A87:A93"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A52:A58"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="A80:A86"/>
     <mergeCell ref="B80:C80"/>
@@ -2277,130 +2260,126 @@
     <mergeCell ref="B63:C63"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="A66:A72"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A52:A58"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="A94:A100"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="A26:A40"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
-    <cfRule type="containsText" dxfId="23" priority="24" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26 D6:D15 D17:D20 D22:D24">
-    <cfRule type="containsText" dxfId="22" priority="23" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D26:D39 D41:D50">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D52:D57">
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D52)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:D64">
-    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D59)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D66:D71">
-    <cfRule type="containsText" dxfId="15" priority="7" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D66)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="8" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D66)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D73:D78">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D73)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D73)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D80:D85">
-    <cfRule type="containsText" dxfId="11" priority="15" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D80)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="16" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D80)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D87:D92">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D87)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="14" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D87)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D94:D99">
-    <cfRule type="containsText" dxfId="7" priority="11" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D94)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="12" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D94)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D101">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="Terminé">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D101)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="En cours">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D101)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED819A8-5EE4-4FDA-9FC8-59367FEA6138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B87F49F-D76D-412D-98D0-FB6ED8E2BFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="8" r:id="rId1"/>
@@ -198,11 +198,6 @@
     <t>Et c'est là ou le fun commence ! J'aime les problèmes ! Tant que je ne casse pas quelque chose de critique… Mais même là, le cluster fait que je réplique tout sur 3 machines, c'est largement récupérable.</t>
   </si>
   <si>
-    <t>J'ai posé la question suivante lors de la préparation de la machine: "Bonjour,
-Je suis en train de Sysprep le server windows, est-ce qu'il y a des programmes spécifiques voulus par l'EMF ? Ou alors un fond d'écran personnalisé ? Ou alors des documents qui devraient être présents, comme les bonnes pratiques ou autre ?
-Le cahier des charges ne spécifie rien de particulier, seulement que la VM doit être aux standards prédéfinis. J'ai donc déjà suivi les standards d'entreprise."</t>
-  </si>
-  <si>
     <t>Créer Template</t>
   </si>
   <si>
@@ -250,6 +245,9 @@
   </si>
   <si>
     <t>Recréer un sysprep de windows server: Problème et solution au point 6.2.5</t>
+  </si>
+  <si>
+    <t>Extrêment frustrant l'expérience Sysprep avec Windows… Comme tout ce que je fait avec Windows pour être honnête. C'est contre mon gré…</t>
   </si>
 </sst>
 </file>
@@ -585,6 +583,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -594,10 +628,86 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -609,124 +719,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1326,45 +1324,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="39"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="42">
         <v>46153</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -1376,7 +1374,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
@@ -1386,7 +1384,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="14"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
@@ -1396,7 +1394,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
@@ -1406,7 +1404,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
@@ -1416,7 +1414,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
@@ -1426,7 +1424,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="14"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
@@ -1436,19 +1434,19 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1461,15 +1459,15 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
+      <c r="A17" s="22">
         <v>46154</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -1481,7 +1479,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
@@ -1491,7 +1489,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
@@ -1501,7 +1499,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>21</v>
       </c>
@@ -1511,24 +1509,24 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="14"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="14"/>
+      <c r="A23" s="23"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1541,15 +1539,15 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="19" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="21"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
+      <c r="A26" s="22">
         <v>46157</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -1561,7 +1559,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
+      <c r="A27" s="23"/>
       <c r="B27" s="15" t="s">
         <v>24</v>
       </c>
@@ -1571,7 +1569,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="15" t="s">
         <v>25</v>
       </c>
@@ -1581,7 +1579,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="14"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="15" t="s">
         <v>26</v>
       </c>
@@ -1591,7 +1589,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="14"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>28</v>
       </c>
@@ -1601,7 +1599,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>27</v>
       </c>
@@ -1611,7 +1609,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
@@ -1621,7 +1619,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="14"/>
+      <c r="A33" s="23"/>
       <c r="B33" s="15" t="s">
         <v>30</v>
       </c>
@@ -1631,45 +1629,45 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="22" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="23"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="34" t="s">
+      <c r="A35" s="23"/>
+      <c r="B35" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="35"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="14"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="14"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="14"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="14"/>
+      <c r="A39" s="23"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1682,27 +1680,27 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="14"/>
-      <c r="B40" s="19" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="26"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13">
+      <c r="A41" s="22">
         <v>46160</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="25"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="14"/>
+      <c r="A42" s="23"/>
       <c r="B42" s="15" t="s">
         <v>34</v>
       </c>
@@ -1712,7 +1710,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="14"/>
+      <c r="A43" s="23"/>
       <c r="B43" s="15" t="s">
         <v>35</v>
       </c>
@@ -1722,7 +1720,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="14"/>
+      <c r="A44" s="23"/>
       <c r="B44" s="15" t="s">
         <v>36</v>
       </c>
@@ -1732,7 +1730,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="14"/>
+      <c r="A45" s="23"/>
       <c r="B45" s="15" t="s">
         <v>37</v>
       </c>
@@ -1742,7 +1740,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="14"/>
+      <c r="A46" s="23"/>
       <c r="B46" s="15" t="s">
         <v>38</v>
       </c>
@@ -1752,25 +1750,25 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="14"/>
+      <c r="A47" s="23"/>
       <c r="B47" s="15"/>
       <c r="C47" s="16"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="15"/>
       <c r="C48" s="16"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="14"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="33"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="14"/>
+      <c r="A50" s="23"/>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1783,15 +1781,15 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="26" t="s">
+      <c r="A51" s="27"/>
+      <c r="B51" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="13">
+      <c r="A52" s="22">
         <v>46161</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -1803,9 +1801,9 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="14"/>
+      <c r="A53" s="23"/>
       <c r="B53" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="16"/>
       <c r="D53" s="8">
@@ -1813,9 +1811,9 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="14"/>
+      <c r="A54" s="23"/>
       <c r="B54" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" s="16"/>
       <c r="D54" s="8">
@@ -1823,19 +1821,19 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="14"/>
+      <c r="A55" s="23"/>
       <c r="B55" s="15"/>
       <c r="C55" s="16"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="14"/>
+      <c r="A56" s="23"/>
       <c r="B56" s="15"/>
       <c r="C56" s="16"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="14"/>
+      <c r="A57" s="23"/>
       <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1847,40 +1845,40 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="28"/>
+    <row r="58" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="27"/>
+      <c r="B58" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="13">
+      <c r="A59" s="22">
         <v>46163</v>
       </c>
-      <c r="B59" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C59" s="35"/>
+      <c r="B59" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C59" s="29"/>
       <c r="D59" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="14"/>
-      <c r="B60" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C60" s="35"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60" s="29"/>
       <c r="D60" s="8">
         <v>1.9</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="14"/>
+      <c r="A61" s="23"/>
       <c r="B61" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C61" s="16"/>
       <c r="D61" s="8">
@@ -1888,19 +1886,19 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="14"/>
+      <c r="A62" s="23"/>
       <c r="B62" s="15"/>
       <c r="C62" s="16"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="14"/>
+      <c r="A63" s="23"/>
       <c r="B63" s="15"/>
       <c r="C63" s="16"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="14"/>
+      <c r="A64" s="23"/>
       <c r="B64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1913,29 +1911,29 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
-      <c r="B65" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" s="27"/>
-      <c r="D65" s="28"/>
+      <c r="A65" s="27"/>
+      <c r="B65" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="13">
+      <c r="A66" s="22">
         <v>46164</v>
       </c>
-      <c r="B66" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C66" s="31"/>
+      <c r="B66" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C66" s="44"/>
       <c r="D66" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
+      <c r="A67" s="23"/>
       <c r="B67" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C67" s="16"/>
       <c r="D67" s="8">
@@ -1943,29 +1941,29 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="14"/>
-      <c r="B68" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C68" s="25"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68" s="31"/>
       <c r="D68" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="14"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="15"/>
       <c r="C69" s="16"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="14"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="33"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="14"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="14"/>
+      <c r="A71" s="23"/>
       <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
@@ -1978,43 +1976,43 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="29"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="28"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="34"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="13"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="31"/>
+      <c r="A73" s="22"/>
+      <c r="B73" s="43"/>
+      <c r="C73" s="44"/>
       <c r="D73" s="7"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="14"/>
+      <c r="A74" s="23"/>
       <c r="B74" s="15"/>
       <c r="C74" s="16"/>
       <c r="D74" s="8"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="14"/>
+      <c r="A75" s="23"/>
       <c r="B75" s="15"/>
       <c r="C75" s="16"/>
       <c r="D75" s="8"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
+      <c r="A76" s="23"/>
       <c r="B76" s="15"/>
       <c r="C76" s="16"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="14"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="33"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="14"/>
+      <c r="A78" s="23"/>
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
@@ -2027,43 +2025,43 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="29"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="28"/>
+      <c r="A79" s="27"/>
+      <c r="B79" s="32"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="34"/>
     </row>
     <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="13"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="31"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="44"/>
       <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="14"/>
+      <c r="A81" s="23"/>
       <c r="B81" s="15"/>
       <c r="C81" s="16"/>
       <c r="D81" s="8"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="14"/>
+      <c r="A82" s="23"/>
       <c r="B82" s="15"/>
       <c r="C82" s="16"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="14"/>
+      <c r="A83" s="23"/>
       <c r="B83" s="15"/>
       <c r="C83" s="16"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="14"/>
+      <c r="A84" s="23"/>
       <c r="B84" s="15"/>
       <c r="C84" s="16"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="14"/>
+      <c r="A85" s="23"/>
       <c r="B85" s="2" t="s">
         <v>6</v>
       </c>
@@ -2076,43 +2074,43 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="14"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="21"/>
+      <c r="A86" s="23"/>
+      <c r="B86" s="24"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="26"/>
     </row>
     <row r="87" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="13"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="31"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="43"/>
+      <c r="C87" s="44"/>
       <c r="D87" s="7"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="14"/>
+      <c r="A88" s="23"/>
       <c r="B88" s="15"/>
       <c r="C88" s="16"/>
       <c r="D88" s="8"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="14"/>
+      <c r="A89" s="23"/>
       <c r="B89" s="15"/>
       <c r="C89" s="16"/>
       <c r="D89" s="8"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="14"/>
+      <c r="A90" s="23"/>
       <c r="B90" s="15"/>
       <c r="C90" s="16"/>
       <c r="D90" s="8"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="14"/>
+      <c r="A91" s="23"/>
       <c r="B91" s="15"/>
       <c r="C91" s="16"/>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="14"/>
+      <c r="A92" s="23"/>
       <c r="B92" s="2" t="s">
         <v>6</v>
       </c>
@@ -2125,43 +2123,43 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="29"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="28"/>
+      <c r="A93" s="27"/>
+      <c r="B93" s="32"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="34"/>
     </row>
     <row r="94" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="13"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="31"/>
+      <c r="A94" s="22"/>
+      <c r="B94" s="43"/>
+      <c r="C94" s="44"/>
       <c r="D94" s="7"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="14"/>
+      <c r="A95" s="23"/>
       <c r="B95" s="15"/>
       <c r="C95" s="16"/>
       <c r="D95" s="8"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="14"/>
+      <c r="A96" s="23"/>
       <c r="B96" s="15"/>
       <c r="C96" s="16"/>
       <c r="D96" s="8"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="14"/>
+      <c r="A97" s="23"/>
       <c r="B97" s="15"/>
       <c r="C97" s="16"/>
       <c r="D97" s="8"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="14"/>
+      <c r="A98" s="23"/>
       <c r="B98" s="15"/>
       <c r="C98" s="16"/>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="14"/>
+      <c r="A99" s="23"/>
       <c r="B99" s="2" t="s">
         <v>6</v>
       </c>
@@ -2174,10 +2172,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="29"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="27"/>
-      <c r="D100" s="28"/>
+      <c r="A100" s="27"/>
+      <c r="B100" s="32"/>
+      <c r="C100" s="33"/>
+      <c r="D100" s="34"/>
     </row>
     <row r="101" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="11"/>
@@ -2191,24 +2189,90 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="44" t="s">
+      <c r="A102" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B102" s="44"/>
-      <c r="C102" s="44"/>
-      <c r="D102" s="44"/>
+      <c r="B102" s="21"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A26:A40"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A94:A100"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="A80:A86"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="A59:A65"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="A66:A72"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A102:D102"/>
     <mergeCell ref="A17:A25"/>
     <mergeCell ref="B17:C17"/>
@@ -2225,81 +2289,15 @@
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="A52:A58"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="A80:A86"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A66:A72"/>
-    <mergeCell ref="A87:A93"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="A94:A100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="A26:A40"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B47:C47"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
     <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B87F49F-D76D-412D-98D0-FB6ED8E2BFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD01D4A-0C4D-4A53-A36C-94CC39FB86D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="8" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -248,6 +248,21 @@
   </si>
   <si>
     <t>Extrêment frustrant l'expérience Sysprep avec Windows… Comme tout ce que je fait avec Windows pour être honnête. C'est contre mon gré…</t>
+  </si>
+  <si>
+    <t>Tests de net-XX : Mauvaises IPs dans le réseau management</t>
+  </si>
+  <si>
+    <t>Je ne souhaite à personne de devoir changer l'IP des nodes d'un cluster Proxmox. Ce n'est pas fondamentalement compliqué, mais suivant comment c'est géré, ça fait paniquer très fort d'avoir tout cassé</t>
+  </si>
+  <si>
+    <t>Mise en place du firewall</t>
+  </si>
+  <si>
+    <t>Tests pve-XX</t>
+  </si>
+  <si>
+    <t>Tests sto-XX</t>
   </si>
 </sst>
 </file>
@@ -583,6 +598,82 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -591,12 +682,48 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -613,118 +740,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1324,45 +1339,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="37"/>
+      <c r="C4" s="39"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
+      <c r="A5" s="40"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42">
+      <c r="A6" s="36">
         <v>46153</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -1374,7 +1389,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
+      <c r="A7" s="14"/>
       <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
@@ -1384,7 +1399,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
@@ -1394,7 +1409,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
+      <c r="A9" s="14"/>
       <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
@@ -1404,7 +1419,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
+      <c r="A10" s="14"/>
       <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
@@ -1414,7 +1429,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
@@ -1424,7 +1439,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
@@ -1434,19 +1449,19 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1459,15 +1474,15 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22">
+      <c r="A17" s="13">
         <v>46154</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -1479,7 +1494,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
+      <c r="A18" s="14"/>
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
@@ -1489,7 +1504,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
@@ -1499,7 +1514,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
+      <c r="A20" s="14"/>
       <c r="B20" s="15" t="s">
         <v>21</v>
       </c>
@@ -1509,24 +1524,24 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="46"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
+      <c r="A23" s="14"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
+      <c r="A24" s="14"/>
       <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1539,15 +1554,15 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24" t="s">
+      <c r="A25" s="14"/>
+      <c r="B25" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="21"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
+      <c r="A26" s="13">
         <v>46157</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -1559,7 +1574,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
+      <c r="A27" s="14"/>
       <c r="B27" s="15" t="s">
         <v>24</v>
       </c>
@@ -1569,7 +1584,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
+      <c r="A28" s="14"/>
       <c r="B28" s="15" t="s">
         <v>25</v>
       </c>
@@ -1579,7 +1594,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
+      <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>26</v>
       </c>
@@ -1589,7 +1604,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
+      <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>28</v>
       </c>
@@ -1599,7 +1614,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
+      <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>27</v>
       </c>
@@ -1609,7 +1624,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
+      <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
@@ -1619,7 +1634,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="14"/>
       <c r="B33" s="15" t="s">
         <v>30</v>
       </c>
@@ -1629,45 +1644,45 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
-      <c r="B34" s="47" t="s">
+      <c r="A34" s="14"/>
+      <c r="B34" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="48"/>
+      <c r="C34" s="23"/>
       <c r="D34" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
-      <c r="B35" s="28" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="29"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="31"/>
+      <c r="A36" s="14"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
+      <c r="A37" s="14"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
+      <c r="A39" s="14"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1680,27 +1695,27 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="26"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22">
+      <c r="A41" s="13">
         <v>46160</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="31"/>
+      <c r="C41" s="25"/>
       <c r="D41" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
+      <c r="A42" s="14"/>
       <c r="B42" s="15" t="s">
         <v>34</v>
       </c>
@@ -1710,7 +1725,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
+      <c r="A43" s="14"/>
       <c r="B43" s="15" t="s">
         <v>35</v>
       </c>
@@ -1720,7 +1735,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
+      <c r="A44" s="14"/>
       <c r="B44" s="15" t="s">
         <v>36</v>
       </c>
@@ -1730,7 +1745,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="15" t="s">
         <v>37</v>
       </c>
@@ -1740,7 +1755,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
+      <c r="A46" s="14"/>
       <c r="B46" s="15" t="s">
         <v>38</v>
       </c>
@@ -1750,25 +1765,25 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
+      <c r="A47" s="14"/>
       <c r="B47" s="15"/>
       <c r="C47" s="16"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="23"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="15"/>
       <c r="C48" s="16"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="23"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="33"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="23"/>
+      <c r="A50" s="14"/>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1781,15 +1796,15 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="27"/>
-      <c r="B51" s="32" t="s">
+      <c r="A51" s="29"/>
+      <c r="B51" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="34"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="28"/>
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="22">
+      <c r="A52" s="13">
         <v>46161</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -1801,7 +1816,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="23"/>
+      <c r="A53" s="14"/>
       <c r="B53" s="15" t="s">
         <v>41</v>
       </c>
@@ -1811,7 +1826,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="23"/>
+      <c r="A54" s="14"/>
       <c r="B54" s="15" t="s">
         <v>45</v>
       </c>
@@ -1821,19 +1836,19 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="23"/>
+      <c r="A55" s="14"/>
       <c r="B55" s="15"/>
       <c r="C55" s="16"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="23"/>
+      <c r="A56" s="14"/>
       <c r="B56" s="15"/>
       <c r="C56" s="16"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="23"/>
+      <c r="A57" s="14"/>
       <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1846,37 +1861,37 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="32" t="s">
+      <c r="A58" s="29"/>
+      <c r="B58" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="34"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="28"/>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22">
+      <c r="A59" s="13">
         <v>46163</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="29"/>
+      <c r="C59" s="35"/>
       <c r="D59" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="23"/>
-      <c r="B60" s="28" t="s">
+      <c r="A60" s="14"/>
+      <c r="B60" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="29"/>
+      <c r="C60" s="35"/>
       <c r="D60" s="8">
         <v>1.9</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
+      <c r="A61" s="14"/>
       <c r="B61" s="15" t="s">
         <v>46</v>
       </c>
@@ -1886,19 +1901,19 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
+      <c r="A62" s="14"/>
       <c r="B62" s="15"/>
       <c r="C62" s="16"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="23"/>
+      <c r="A63" s="14"/>
       <c r="B63" s="15"/>
       <c r="C63" s="16"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
+      <c r="A64" s="14"/>
       <c r="B64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1911,27 +1926,27 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="27"/>
-      <c r="B65" s="32" t="s">
+      <c r="A65" s="29"/>
+      <c r="B65" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="33"/>
-      <c r="D65" s="34"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="28"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="22">
+      <c r="A66" s="13">
         <v>46164</v>
       </c>
-      <c r="B66" s="43" t="s">
+      <c r="B66" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="44"/>
+      <c r="C66" s="31"/>
       <c r="D66" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
+      <c r="A67" s="14"/>
       <c r="B67" s="15" t="s">
         <v>48</v>
       </c>
@@ -1941,29 +1956,29 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="23"/>
-      <c r="B68" s="30" t="s">
+      <c r="A68" s="14"/>
+      <c r="B68" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="C68" s="31"/>
+      <c r="C68" s="25"/>
       <c r="D68" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="14"/>
       <c r="B69" s="15"/>
       <c r="C69" s="16"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="23"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="14"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="33"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="23"/>
+      <c r="A71" s="14"/>
       <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
@@ -1976,43 +1991,61 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="27"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="34"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="28"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="22"/>
-      <c r="B73" s="43"/>
-      <c r="C73" s="44"/>
-      <c r="D73" s="7"/>
+      <c r="A73" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C73" s="35"/>
+      <c r="D73" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="23"/>
-      <c r="B74" s="15"/>
+      <c r="A74" s="14"/>
+      <c r="B74" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="C74" s="16"/>
-      <c r="D74" s="8"/>
+      <c r="D74" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
-      <c r="B75" s="15"/>
+      <c r="A75" s="14"/>
+      <c r="B75" s="15" t="s">
+        <v>54</v>
+      </c>
       <c r="C75" s="16"/>
-      <c r="D75" s="8"/>
+      <c r="D75" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="23"/>
-      <c r="B76" s="15"/>
+      <c r="A76" s="14"/>
+      <c r="B76" s="15" t="s">
+        <v>55</v>
+      </c>
       <c r="C76" s="16"/>
-      <c r="D76" s="8"/>
+      <c r="D76" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="23"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="14"/>
+      <c r="A77" s="14"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="33"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="23"/>
+      <c r="A78" s="14"/>
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
@@ -2021,47 +2054,49 @@
       </c>
       <c r="D78" s="9">
         <f>SUM(D73:D77)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="27"/>
-      <c r="B79" s="32"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="34"/>
+      <c r="A79" s="29"/>
+      <c r="B79" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" s="27"/>
+      <c r="D79" s="28"/>
     </row>
     <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="22"/>
-      <c r="B80" s="43"/>
-      <c r="C80" s="44"/>
+      <c r="A80" s="13"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="31"/>
       <c r="D80" s="7"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="23"/>
+      <c r="A81" s="14"/>
       <c r="B81" s="15"/>
       <c r="C81" s="16"/>
       <c r="D81" s="8"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="23"/>
+      <c r="A82" s="14"/>
       <c r="B82" s="15"/>
       <c r="C82" s="16"/>
       <c r="D82" s="8"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="23"/>
+      <c r="A83" s="14"/>
       <c r="B83" s="15"/>
       <c r="C83" s="16"/>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="23"/>
+      <c r="A84" s="14"/>
       <c r="B84" s="15"/>
       <c r="C84" s="16"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="23"/>
+      <c r="A85" s="14"/>
       <c r="B85" s="2" t="s">
         <v>6</v>
       </c>
@@ -2074,43 +2109,43 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="23"/>
-      <c r="B86" s="24"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="26"/>
+      <c r="A86" s="14"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="21"/>
     </row>
     <row r="87" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="22"/>
-      <c r="B87" s="43"/>
-      <c r="C87" s="44"/>
+      <c r="A87" s="13"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="31"/>
       <c r="D87" s="7"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="23"/>
+      <c r="A88" s="14"/>
       <c r="B88" s="15"/>
       <c r="C88" s="16"/>
       <c r="D88" s="8"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="23"/>
+      <c r="A89" s="14"/>
       <c r="B89" s="15"/>
       <c r="C89" s="16"/>
       <c r="D89" s="8"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="23"/>
+      <c r="A90" s="14"/>
       <c r="B90" s="15"/>
       <c r="C90" s="16"/>
       <c r="D90" s="8"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="23"/>
+      <c r="A91" s="14"/>
       <c r="B91" s="15"/>
       <c r="C91" s="16"/>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="23"/>
+      <c r="A92" s="14"/>
       <c r="B92" s="2" t="s">
         <v>6</v>
       </c>
@@ -2123,43 +2158,43 @@
       </c>
     </row>
     <row r="93" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="27"/>
-      <c r="B93" s="32"/>
-      <c r="C93" s="33"/>
-      <c r="D93" s="34"/>
+      <c r="A93" s="29"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="28"/>
     </row>
     <row r="94" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="22"/>
-      <c r="B94" s="43"/>
-      <c r="C94" s="44"/>
+      <c r="A94" s="13"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="31"/>
       <c r="D94" s="7"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="23"/>
+      <c r="A95" s="14"/>
       <c r="B95" s="15"/>
       <c r="C95" s="16"/>
       <c r="D95" s="8"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="23"/>
+      <c r="A96" s="14"/>
       <c r="B96" s="15"/>
       <c r="C96" s="16"/>
       <c r="D96" s="8"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="23"/>
+      <c r="A97" s="14"/>
       <c r="B97" s="15"/>
       <c r="C97" s="16"/>
       <c r="D97" s="8"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="23"/>
+      <c r="A98" s="14"/>
       <c r="B98" s="15"/>
       <c r="C98" s="16"/>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="23"/>
+      <c r="A99" s="14"/>
       <c r="B99" s="2" t="s">
         <v>6</v>
       </c>
@@ -2172,10 +2207,10 @@
       </c>
     </row>
     <row r="100" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="27"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="33"/>
-      <c r="D100" s="34"/>
+      <c r="A100" s="29"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="27"/>
+      <c r="D100" s="28"/>
     </row>
     <row r="101" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="11"/>
@@ -2185,59 +2220,63 @@
       </c>
       <c r="D101" s="12">
         <f>D15+D24+D39+D50+D57+D64+D71+D78+D85+D92+D99</f>
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="21" t="s">
+      <c r="A102" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B102" s="21"/>
-      <c r="C102" s="21"/>
-      <c r="D102" s="21"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A26:A40"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A94:A100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="A87:A93"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A52:A58"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="A80:A86"/>
     <mergeCell ref="B80:C80"/>
@@ -2254,50 +2293,46 @@
     <mergeCell ref="B63:C63"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="A66:A72"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A52:A58"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A87:A93"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="A94:A100"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="A26:A40"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
     <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD01D4A-0C4D-4A53-A36C-94CC39FB86D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8380C0E-DF97-4C64-8687-98AE24669609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="8" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -244,25 +244,53 @@
     <t>Créer le playbook pour supprimmer des VMs</t>
   </si>
   <si>
-    <t>Recréer un sysprep de windows server: Problème et solution au point 6.2.5</t>
-  </si>
-  <si>
     <t>Extrêment frustrant l'expérience Sysprep avec Windows… Comme tout ce que je fait avec Windows pour être honnête. C'est contre mon gré…</t>
   </si>
   <si>
-    <t>Tests de net-XX : Mauvaises IPs dans le réseau management</t>
-  </si>
-  <si>
     <t>Je ne souhaite à personne de devoir changer l'IP des nodes d'un cluster Proxmox. Ce n'est pas fondamentalement compliqué, mais suivant comment c'est géré, ça fait paniquer très fort d'avoir tout cassé</t>
   </si>
   <si>
     <t>Mise en place du firewall</t>
   </si>
   <si>
-    <t>Tests pve-XX</t>
-  </si>
-  <si>
-    <t>Tests sto-XX</t>
+    <t>Tests</t>
+  </si>
+  <si>
+    <t>Documentation des problèmes</t>
+  </si>
+  <si>
+    <r>
+      <t>Recréer un sysprep de windows server:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Problème et solution au point 6.2.5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tests de net-XX : Mauvaises IPs dans le réseau management:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Problème et solution au point 6.2.6</t>
+    </r>
+  </si>
+  <si>
+    <t>Rendez-vous expert + PV</t>
+  </si>
+  <si>
+    <t>Manuel utilisateur</t>
   </si>
 </sst>
 </file>
@@ -273,7 +301,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -345,6 +373,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -598,6 +632,42 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -607,10 +677,86 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -622,124 +768,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1328,7 +1362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1339,45 +1373,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="39"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36">
+      <c r="A6" s="42">
         <v>46153</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -1389,7 +1423,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="15" t="s">
         <v>9</v>
       </c>
@@ -1399,7 +1433,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="14"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="15" t="s">
         <v>10</v>
       </c>
@@ -1409,7 +1443,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="14"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="15" t="s">
         <v>14</v>
       </c>
@@ -1419,7 +1453,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="15" t="s">
         <v>11</v>
       </c>
@@ -1429,7 +1463,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
@@ -1439,7 +1473,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="14"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="15" t="s">
         <v>13</v>
       </c>
@@ -1449,19 +1483,19 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
+      <c r="A15" s="23"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1474,15 +1508,15 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="19" t="s">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="26"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
+      <c r="A17" s="22">
         <v>46154</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -1494,7 +1528,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="15" t="s">
         <v>17</v>
       </c>
@@ -1504,7 +1538,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="15" t="s">
         <v>18</v>
       </c>
@@ -1514,7 +1548,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="15" t="s">
         <v>21</v>
       </c>
@@ -1524,24 +1558,24 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="14"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="14"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="46"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="14"/>
+      <c r="A23" s="23"/>
       <c r="B23" s="15"/>
       <c r="C23" s="16"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1554,15 +1588,15 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
-      <c r="B25" s="19" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="21"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
+      <c r="A26" s="22">
         <v>46157</v>
       </c>
       <c r="B26" s="15" t="s">
@@ -1574,7 +1608,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
+      <c r="A27" s="23"/>
       <c r="B27" s="15" t="s">
         <v>24</v>
       </c>
@@ -1584,7 +1618,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="15" t="s">
         <v>25</v>
       </c>
@@ -1594,7 +1628,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="14"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="15" t="s">
         <v>26</v>
       </c>
@@ -1604,7 +1638,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="14"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="15" t="s">
         <v>28</v>
       </c>
@@ -1614,7 +1648,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="15" t="s">
         <v>27</v>
       </c>
@@ -1624,7 +1658,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
@@ -1634,7 +1668,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="14"/>
+      <c r="A33" s="23"/>
       <c r="B33" s="15" t="s">
         <v>30</v>
       </c>
@@ -1644,45 +1678,45 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="14"/>
-      <c r="B34" s="22" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="23"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="34" t="s">
+      <c r="A35" s="23"/>
+      <c r="B35" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="35"/>
+      <c r="C35" s="29"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="14"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="31"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="14"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="18"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="46"/>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="14"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="18"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="46"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="14"/>
+      <c r="A39" s="23"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1695,27 +1729,27 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="14"/>
-      <c r="B40" s="19" t="s">
+      <c r="A40" s="23"/>
+      <c r="B40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="21"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="26"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13">
+      <c r="A41" s="22">
         <v>46160</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="25"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="14"/>
+      <c r="A42" s="23"/>
       <c r="B42" s="15" t="s">
         <v>34</v>
       </c>
@@ -1725,7 +1759,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="14"/>
+      <c r="A43" s="23"/>
       <c r="B43" s="15" t="s">
         <v>35</v>
       </c>
@@ -1735,7 +1769,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="14"/>
+      <c r="A44" s="23"/>
       <c r="B44" s="15" t="s">
         <v>36</v>
       </c>
@@ -1745,7 +1779,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="14"/>
+      <c r="A45" s="23"/>
       <c r="B45" s="15" t="s">
         <v>37</v>
       </c>
@@ -1755,7 +1789,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="14"/>
+      <c r="A46" s="23"/>
       <c r="B46" s="15" t="s">
         <v>38</v>
       </c>
@@ -1765,25 +1799,25 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="14"/>
+      <c r="A47" s="23"/>
       <c r="B47" s="15"/>
       <c r="C47" s="16"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="15"/>
       <c r="C48" s="16"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="14"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="33"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="14"/>
+      <c r="A50" s="23"/>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1796,15 +1830,15 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="29"/>
-      <c r="B51" s="26" t="s">
+      <c r="A51" s="27"/>
+      <c r="B51" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="27"/>
-      <c r="D51" s="28"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="13">
+      <c r="A52" s="22">
         <v>46161</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -1816,7 +1850,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="14"/>
+      <c r="A53" s="23"/>
       <c r="B53" s="15" t="s">
         <v>41</v>
       </c>
@@ -1826,7 +1860,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="14"/>
+      <c r="A54" s="23"/>
       <c r="B54" s="15" t="s">
         <v>45</v>
       </c>
@@ -1836,19 +1870,19 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="14"/>
+      <c r="A55" s="23"/>
       <c r="B55" s="15"/>
       <c r="C55" s="16"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="14"/>
+      <c r="A56" s="23"/>
       <c r="B56" s="15"/>
       <c r="C56" s="16"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="14"/>
+      <c r="A57" s="23"/>
       <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1861,37 +1895,37 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="29"/>
-      <c r="B58" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C58" s="27"/>
-      <c r="D58" s="28"/>
+      <c r="A58" s="27"/>
+      <c r="B58" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="13">
+      <c r="A59" s="22">
         <v>46163</v>
       </c>
-      <c r="B59" s="34" t="s">
+      <c r="B59" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="35"/>
+      <c r="C59" s="29"/>
       <c r="D59" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="14"/>
-      <c r="B60" s="34" t="s">
+      <c r="A60" s="23"/>
+      <c r="B60" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="35"/>
+      <c r="C60" s="29"/>
       <c r="D60" s="8">
         <v>1.9</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="14"/>
+      <c r="A61" s="23"/>
       <c r="B61" s="15" t="s">
         <v>46</v>
       </c>
@@ -1901,19 +1935,19 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="14"/>
+      <c r="A62" s="23"/>
       <c r="B62" s="15"/>
       <c r="C62" s="16"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="14"/>
+      <c r="A63" s="23"/>
       <c r="B63" s="15"/>
       <c r="C63" s="16"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="14"/>
+      <c r="A64" s="23"/>
       <c r="B64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1926,27 +1960,27 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="29"/>
-      <c r="B65" s="26" t="s">
+      <c r="A65" s="27"/>
+      <c r="B65" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="27"/>
-      <c r="D65" s="28"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="34"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="13">
+      <c r="A66" s="22">
         <v>46164</v>
       </c>
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="31"/>
+      <c r="C66" s="44"/>
       <c r="D66" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
+      <c r="A67" s="23"/>
       <c r="B67" s="15" t="s">
         <v>48</v>
       </c>
@@ -1956,29 +1990,29 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="14"/>
-      <c r="B68" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C68" s="25"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="31"/>
       <c r="D68" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="14"/>
+      <c r="A69" s="23"/>
       <c r="B69" s="15"/>
       <c r="C69" s="16"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="14"/>
-      <c r="B70" s="32"/>
-      <c r="C70" s="33"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="14"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="14"/>
+      <c r="A71" s="23"/>
       <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
@@ -1991,27 +2025,27 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="29"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="28"/>
+      <c r="A72" s="27"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="34"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="13">
+      <c r="A73" s="22">
         <v>46171</v>
       </c>
-      <c r="B73" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="C73" s="35"/>
+      <c r="B73" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C73" s="29"/>
       <c r="D73" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="14"/>
+      <c r="A74" s="23"/>
       <c r="B74" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C74" s="16"/>
       <c r="D74" s="8">
@@ -2019,33 +2053,29 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="14"/>
+      <c r="A75" s="23"/>
       <c r="B75" s="15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C75" s="16"/>
       <c r="D75" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="14"/>
-      <c r="B76" s="15" t="s">
-        <v>55</v>
-      </c>
+      <c r="A76" s="23"/>
+      <c r="B76" s="15"/>
       <c r="C76" s="16"/>
-      <c r="D76" s="8">
-        <v>2</v>
-      </c>
+      <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="14"/>
-      <c r="B77" s="32"/>
-      <c r="C77" s="33"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="13"/>
+      <c r="C77" s="14"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="14"/>
+      <c r="A78" s="23"/>
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
@@ -2058,191 +2088,300 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="29"/>
-      <c r="B79" s="26" t="s">
+      <c r="A79" s="27"/>
+      <c r="B79" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C79" s="33"/>
+      <c r="D79" s="34"/>
+    </row>
+    <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="22">
+        <v>46174</v>
+      </c>
+      <c r="B80" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="C79" s="27"/>
-      <c r="D79" s="28"/>
-    </row>
-    <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="13"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="31"/>
-      <c r="D80" s="7"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="14"/>
-      <c r="B81" s="15"/>
+      <c r="A81" s="23"/>
+      <c r="B81" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="C81" s="16"/>
-      <c r="D81" s="8"/>
+      <c r="D81" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="14"/>
-      <c r="B82" s="15"/>
+      <c r="A82" s="23"/>
+      <c r="B82" s="15" t="s">
+        <v>56</v>
+      </c>
       <c r="C82" s="16"/>
-      <c r="D82" s="8"/>
+      <c r="D82" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="14"/>
-      <c r="B83" s="15"/>
+      <c r="A83" s="23"/>
+      <c r="B83" s="15" t="s">
+        <v>57</v>
+      </c>
       <c r="C83" s="16"/>
-      <c r="D83" s="8"/>
+      <c r="D83" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="14"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="16"/>
+      <c r="A84" s="23"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="18"/>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="14"/>
-      <c r="B85" s="2" t="s">
+      <c r="A85" s="23"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="23"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="23"/>
+      <c r="B87" s="15"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="8"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="23"/>
+      <c r="B88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D85" s="9">
-        <f>SUM(D80:D84)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="14"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="21"/>
-    </row>
-    <row r="87" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="13"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="31"/>
-      <c r="D87" s="7"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="14"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="16"/>
-      <c r="D88" s="8"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="14"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="8"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="14"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="8"/>
+      <c r="D88" s="9">
+        <f>SUM(D80:D87)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="23"/>
+      <c r="B89" s="24"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="26"/>
+    </row>
+    <row r="90" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="22">
+        <v>46175</v>
+      </c>
+      <c r="B90" s="43"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="7"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="14"/>
+      <c r="A91" s="23"/>
       <c r="B91" s="15"/>
       <c r="C91" s="16"/>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="14"/>
-      <c r="B92" s="2" t="s">
+      <c r="A92" s="23"/>
+      <c r="B92" s="15"/>
+      <c r="C92" s="16"/>
+      <c r="D92" s="8"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="23"/>
+      <c r="B93" s="15"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="8"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="23"/>
+      <c r="B94" s="15"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="8"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="23"/>
+      <c r="B95" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D92" s="9">
-        <f>SUM(D87:D91)</f>
+      <c r="D95" s="9">
+        <f>SUM(D90:D94)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="29"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="27"/>
-      <c r="D93" s="28"/>
-    </row>
-    <row r="94" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="13"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="31"/>
-      <c r="D94" s="7"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="14"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="16"/>
-      <c r="D95" s="8"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="14"/>
-      <c r="B96" s="15"/>
-      <c r="C96" s="16"/>
-      <c r="D96" s="8"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="14"/>
-      <c r="B97" s="15"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="8"/>
+    <row r="96" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="27"/>
+      <c r="B96" s="32"/>
+      <c r="C96" s="33"/>
+      <c r="D96" s="34"/>
+    </row>
+    <row r="97" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="22">
+        <v>46178</v>
+      </c>
+      <c r="B97" s="43"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="7"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="14"/>
+      <c r="A98" s="23"/>
       <c r="B98" s="15"/>
       <c r="C98" s="16"/>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="14"/>
-      <c r="B99" s="2" t="s">
+      <c r="A99" s="23"/>
+      <c r="B99" s="15"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="8"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="23"/>
+      <c r="B100" s="15"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="8"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="23"/>
+      <c r="B101" s="15"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="8"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="23"/>
+      <c r="B102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D99" s="9">
-        <f>SUM(D94:D98)</f>
+      <c r="D102" s="9">
+        <f>SUM(D97:D101)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="29"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="27"/>
-      <c r="D100" s="28"/>
-    </row>
-    <row r="101" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="11"/>
-      <c r="B101" s="10"/>
-      <c r="C101" s="3" t="s">
+    <row r="103" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="27"/>
+      <c r="B103" s="32"/>
+      <c r="C103" s="33"/>
+      <c r="D103" s="34"/>
+    </row>
+    <row r="104" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="11"/>
+      <c r="B104" s="10"/>
+      <c r="C104" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D101" s="12">
-        <f>D15+D24+D39+D50+D57+D64+D71+D78+D85+D92+D99</f>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="44" t="s">
+      <c r="D104" s="12">
+        <f>D15+D24+D39+D50+D57+D64+D71+D78+D88+D95+D102</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B102" s="44"/>
-      <c r="C102" s="44"/>
-      <c r="D102" s="44"/>
+      <c r="B105" s="21"/>
+      <c r="C105" s="21"/>
+      <c r="D105" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="100">
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="A102:D102"/>
+  <mergeCells count="103">
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="A26:A40"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A97:A103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="A90:A96"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B96:D96"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="A80:A89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="A59:A65"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="A66:A72"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A105:D105"/>
     <mergeCell ref="A17:A25"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
@@ -2258,81 +2397,15 @@
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="A52:A58"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="A80:A86"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A66:A72"/>
-    <mergeCell ref="A87:A93"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="A94:A100"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B100:D100"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="A26:A40"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B47:C47"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
     <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">
@@ -2384,7 +2457,7 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D73)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D80:D85">
+  <conditionalFormatting sqref="D80:D88">
     <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D80)))</formula>
     </cfRule>
@@ -2392,28 +2465,28 @@
       <formula>NOT(ISERROR(SEARCH("En cours",D80)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D87:D92">
+  <conditionalFormatting sqref="D90:D95">
     <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D87)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D90)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D87)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D90)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D94:D99">
+  <conditionalFormatting sqref="D97:D102">
     <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D94)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D97)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D94)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D97)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D101">
+  <conditionalFormatting sqref="D104">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D101)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D104)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D101)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D104)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2426,7 +2499,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="65" max="16383" man="1"/>
-    <brk id="101" max="3" man="1"/>
+    <brk id="104" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8380C0E-DF97-4C64-8687-98AE24669609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74D867C-94FE-41BF-980A-02A0F73972D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Manuel utilisateur</t>
+  </si>
+  <si>
+    <t>Documentation</t>
   </si>
 </sst>
 </file>
@@ -632,6 +635,90 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -640,20 +727,48 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -662,118 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1373,129 +1376,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="45"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="37"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="43"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="42">
+      <c r="A6" s="38">
         <v>46153</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="16"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="23"/>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="16"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
-      <c r="B8" s="15" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="16"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="15" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="16"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="23"/>
-      <c r="B10" s="15" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="23"/>
-      <c r="B11" s="15" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="16"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="23"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="23"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="14"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1508,74 +1511,74 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22">
+      <c r="A17" s="15">
         <v>46154</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="16"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
-      <c r="B18" s="15" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="16"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="15" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="16"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="8">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
-      <c r="B20" s="15" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="16"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20"/>
+      <c r="A21" s="16"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="48"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="16"/>
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1588,135 +1591,135 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="23"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="22">
+      <c r="A26" s="15">
         <v>46157</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="16"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="15" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C27" s="16"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
-      <c r="B28" s="15" t="s">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="23"/>
-      <c r="B29" s="15" t="s">
+      <c r="A29" s="16"/>
+      <c r="B29" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="16"/>
+      <c r="C29" s="18"/>
       <c r="D29" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
-      <c r="B30" s="15" t="s">
+      <c r="A30" s="16"/>
+      <c r="B30" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="16"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
-      <c r="B31" s="15" t="s">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="16"/>
+      <c r="C31" s="18"/>
       <c r="D31" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="15" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="16"/>
+      <c r="C32" s="18"/>
       <c r="D32" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="15" t="s">
+      <c r="A33" s="16"/>
+      <c r="B33" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="16"/>
+      <c r="C33" s="18"/>
       <c r="D33" s="8">
         <v>0.3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
-      <c r="B34" s="47" t="s">
+      <c r="A34" s="16"/>
+      <c r="B34" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="48"/>
+      <c r="C34" s="25"/>
       <c r="D34" s="8">
         <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
-      <c r="B35" s="28" t="s">
+      <c r="A35" s="16"/>
+      <c r="B35" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="29"/>
+      <c r="C35" s="33"/>
       <c r="D35" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="31"/>
+      <c r="A36" s="16"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="8"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="46"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="20"/>
       <c r="D37" s="8"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="46"/>
+      <c r="A38" s="16"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
       <c r="D38" s="8"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1729,95 +1732,95 @@
       </c>
     </row>
     <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24" t="s">
+      <c r="A40" s="16"/>
+      <c r="B40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="26"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="23"/>
     </row>
     <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="22">
+      <c r="A41" s="15">
         <v>46160</v>
       </c>
-      <c r="B41" s="30" t="s">
+      <c r="B41" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="31"/>
+      <c r="C41" s="27"/>
       <c r="D41" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
-      <c r="B42" s="15" t="s">
+      <c r="A42" s="16"/>
+      <c r="B42" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="16"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="23"/>
-      <c r="B43" s="15" t="s">
+      <c r="A43" s="16"/>
+      <c r="B43" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="16"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="8">
         <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
-      <c r="B44" s="15" t="s">
+      <c r="A44" s="16"/>
+      <c r="B44" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C44" s="16"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
-      <c r="B45" s="15" t="s">
+      <c r="A45" s="16"/>
+      <c r="B45" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C45" s="16"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
-      <c r="B46" s="15" t="s">
+      <c r="A46" s="16"/>
+      <c r="B46" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="16"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="23"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="23"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="16"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
       <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="23"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="35"/>
       <c r="D49" s="8"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="23"/>
+      <c r="A50" s="16"/>
       <c r="B50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1830,59 +1833,59 @@
       </c>
     </row>
     <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="27"/>
-      <c r="B51" s="32" t="s">
+      <c r="A51" s="31"/>
+      <c r="B51" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="33"/>
-      <c r="D51" s="34"/>
+      <c r="C51" s="29"/>
+      <c r="D51" s="30"/>
     </row>
     <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="22">
+      <c r="A52" s="15">
         <v>46161</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C52" s="16"/>
+      <c r="C52" s="18"/>
       <c r="D52" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="23"/>
-      <c r="B53" s="15" t="s">
+      <c r="A53" s="16"/>
+      <c r="B53" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="16"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="23"/>
-      <c r="B54" s="15" t="s">
+      <c r="A54" s="16"/>
+      <c r="B54" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C54" s="16"/>
+      <c r="C54" s="18"/>
       <c r="D54" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="23"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="16"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
       <c r="D55" s="8"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="23"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="16"/>
+      <c r="A56" s="16"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="18"/>
       <c r="D56" s="8"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="23"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1895,59 +1898,59 @@
       </c>
     </row>
     <row r="58" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="32" t="s">
+      <c r="A58" s="31"/>
+      <c r="B58" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="34"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="30"/>
     </row>
     <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="22">
+      <c r="A59" s="15">
         <v>46163</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="C59" s="29"/>
+      <c r="C59" s="33"/>
       <c r="D59" s="7">
         <v>0.1</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="23"/>
-      <c r="B60" s="28" t="s">
+      <c r="A60" s="16"/>
+      <c r="B60" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="29"/>
+      <c r="C60" s="33"/>
       <c r="D60" s="8">
         <v>1.9</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
-      <c r="B61" s="15" t="s">
+      <c r="A61" s="16"/>
+      <c r="B61" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C61" s="16"/>
+      <c r="C61" s="18"/>
       <c r="D61" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="16"/>
+      <c r="A62" s="16"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="18"/>
       <c r="D62" s="8"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="23"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="16"/>
+      <c r="A63" s="16"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="18"/>
       <c r="D63" s="8"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1960,59 +1963,59 @@
       </c>
     </row>
     <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="27"/>
-      <c r="B65" s="32" t="s">
+      <c r="A65" s="31"/>
+      <c r="B65" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C65" s="33"/>
-      <c r="D65" s="34"/>
+      <c r="C65" s="29"/>
+      <c r="D65" s="30"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="22">
+      <c r="A66" s="15">
         <v>46164</v>
       </c>
-      <c r="B66" s="43" t="s">
+      <c r="B66" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C66" s="44"/>
+      <c r="C66" s="37"/>
       <c r="D66" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
-      <c r="B67" s="15" t="s">
+      <c r="A67" s="16"/>
+      <c r="B67" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C67" s="16"/>
+      <c r="C67" s="18"/>
       <c r="D67" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="23"/>
-      <c r="B68" s="30" t="s">
+      <c r="A68" s="16"/>
+      <c r="B68" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C68" s="31"/>
+      <c r="C68" s="27"/>
       <c r="D68" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="16"/>
+      <c r="A69" s="16"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="18"/>
       <c r="D69" s="8"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="23"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="14"/>
+      <c r="A70" s="16"/>
+      <c r="B70" s="34"/>
+      <c r="C70" s="35"/>
       <c r="D70" s="8"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="23"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="2" t="s">
         <v>6</v>
       </c>
@@ -2025,57 +2028,57 @@
       </c>
     </row>
     <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="27"/>
-      <c r="B72" s="32"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="34"/>
+      <c r="A72" s="31"/>
+      <c r="B72" s="28"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="30"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="22">
+      <c r="A73" s="15">
         <v>46171</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="29"/>
+      <c r="C73" s="33"/>
       <c r="D73" s="7">
         <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="23"/>
-      <c r="B74" s="15" t="s">
+      <c r="A74" s="16"/>
+      <c r="B74" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C74" s="16"/>
+      <c r="C74" s="18"/>
       <c r="D74" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
-      <c r="B75" s="15" t="s">
+      <c r="A75" s="16"/>
+      <c r="B75" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C75" s="16"/>
+      <c r="C75" s="18"/>
       <c r="D75" s="8">
         <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="23"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="16"/>
+      <c r="A76" s="16"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
       <c r="D76" s="8"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="23"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="14"/>
+      <c r="A77" s="16"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="35"/>
       <c r="D77" s="8"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="23"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="2" t="s">
         <v>6</v>
       </c>
@@ -2088,81 +2091,85 @@
       </c>
     </row>
     <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="27"/>
-      <c r="B79" s="32" t="s">
+      <c r="A79" s="31"/>
+      <c r="B79" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C79" s="33"/>
-      <c r="D79" s="34"/>
+      <c r="C79" s="29"/>
+      <c r="D79" s="30"/>
     </row>
     <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="22">
+      <c r="A80" s="15">
         <v>46174</v>
       </c>
-      <c r="B80" s="43" t="s">
+      <c r="B80" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="C80" s="44"/>
+      <c r="C80" s="37"/>
       <c r="D80" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="23"/>
-      <c r="B81" s="15" t="s">
+      <c r="A81" s="16"/>
+      <c r="B81" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C81" s="16"/>
+      <c r="C81" s="18"/>
       <c r="D81" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="23"/>
-      <c r="B82" s="15" t="s">
+      <c r="A82" s="16"/>
+      <c r="B82" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C82" s="16"/>
+      <c r="C82" s="18"/>
       <c r="D82" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="23"/>
-      <c r="B83" s="15" t="s">
+      <c r="A83" s="16"/>
+      <c r="B83" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C83" s="16"/>
+      <c r="C83" s="18"/>
       <c r="D83" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="23"/>
-      <c r="B84" s="17"/>
+      <c r="A84" s="16"/>
+      <c r="B84" s="17" t="s">
+        <v>58</v>
+      </c>
       <c r="C84" s="18"/>
-      <c r="D84" s="8"/>
+      <c r="D84" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="23"/>
+      <c r="A85" s="16"/>
       <c r="B85" s="17"/>
       <c r="C85" s="18"/>
       <c r="D85" s="8"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="23"/>
+      <c r="A86" s="16"/>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
       <c r="D86" s="8"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="23"/>
-      <c r="B87" s="15"/>
-      <c r="C87" s="16"/>
+      <c r="A87" s="16"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="18"/>
       <c r="D87" s="8"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="23"/>
+      <c r="A88" s="16"/>
       <c r="B88" s="2" t="s">
         <v>6</v>
       </c>
@@ -2171,49 +2178,49 @@
       </c>
       <c r="D88" s="9">
         <f>SUM(D80:D87)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="23"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="26"/>
+      <c r="A89" s="16"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="23"/>
     </row>
     <row r="90" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="22">
+      <c r="A90" s="15">
         <v>46175</v>
       </c>
-      <c r="B90" s="43"/>
-      <c r="C90" s="44"/>
+      <c r="B90" s="36"/>
+      <c r="C90" s="37"/>
       <c r="D90" s="7"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="23"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="16"/>
+      <c r="A91" s="16"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="18"/>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="23"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="16"/>
+      <c r="A92" s="16"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="18"/>
       <c r="D92" s="8"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="23"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="16"/>
+      <c r="A93" s="16"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="18"/>
       <c r="D93" s="8"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="23"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="16"/>
+      <c r="A94" s="16"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="18"/>
       <c r="D94" s="8"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="23"/>
+      <c r="A95" s="16"/>
       <c r="B95" s="2" t="s">
         <v>6</v>
       </c>
@@ -2226,45 +2233,45 @@
       </c>
     </row>
     <row r="96" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="27"/>
-      <c r="B96" s="32"/>
-      <c r="C96" s="33"/>
-      <c r="D96" s="34"/>
+      <c r="A96" s="31"/>
+      <c r="B96" s="28"/>
+      <c r="C96" s="29"/>
+      <c r="D96" s="30"/>
     </row>
     <row r="97" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="22">
+      <c r="A97" s="15">
         <v>46178</v>
       </c>
-      <c r="B97" s="43"/>
-      <c r="C97" s="44"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="37"/>
       <c r="D97" s="7"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="23"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="16"/>
+      <c r="A98" s="16"/>
+      <c r="B98" s="17"/>
+      <c r="C98" s="18"/>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="23"/>
-      <c r="B99" s="15"/>
-      <c r="C99" s="16"/>
+      <c r="A99" s="16"/>
+      <c r="B99" s="17"/>
+      <c r="C99" s="18"/>
       <c r="D99" s="8"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="23"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="16"/>
+      <c r="A100" s="16"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="18"/>
       <c r="D100" s="8"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="23"/>
-      <c r="B101" s="15"/>
-      <c r="C101" s="16"/>
+      <c r="A101" s="16"/>
+      <c r="B101" s="17"/>
+      <c r="C101" s="18"/>
       <c r="D101" s="8"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="23"/>
+      <c r="A102" s="16"/>
       <c r="B102" s="2" t="s">
         <v>6</v>
       </c>
@@ -2277,10 +2284,10 @@
       </c>
     </row>
     <row r="103" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="27"/>
-      <c r="B103" s="32"/>
-      <c r="C103" s="33"/>
-      <c r="D103" s="34"/>
+      <c r="A103" s="31"/>
+      <c r="B103" s="28"/>
+      <c r="C103" s="29"/>
+      <c r="D103" s="30"/>
     </row>
     <row r="104" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="11"/>
@@ -2290,19 +2297,98 @@
       </c>
       <c r="D104" s="12">
         <f>D15+D24+D39+D50+D57+D64+D71+D78+D88+D95+D102</f>
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="21" t="s">
+      <c r="A105" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B105" s="21"/>
-      <c r="C105" s="21"/>
-      <c r="D105" s="21"/>
+      <c r="B105" s="46"/>
+      <c r="C105" s="46"/>
+      <c r="D105" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="103">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="A52:A58"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="A80:A89"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="A59:A65"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="A66:A72"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A97:A103"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="A90:A96"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B96:D96"/>
     <mergeCell ref="B84:C84"/>
     <mergeCell ref="B85:C85"/>
     <mergeCell ref="B86:C86"/>
@@ -2327,85 +2413,6 @@
     <mergeCell ref="B76:C76"/>
     <mergeCell ref="B77:C77"/>
     <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A97:A103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="A90:A96"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="A80:A89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A66:A72"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A17:A25"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A41:A51"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A52:A58"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B47:C47"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
     <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">

--- a/Doc/3_CAND_Modele_Journal_2026.xlsx
+++ b/Doc/3_CAND_Modele_Journal_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TPI - 2026 - Lucielle Voeffray\Dossier de projet\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C74D867C-94FE-41BF-980A-02A0F73972D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536FD10C-FB5B-4CB7-A9A4-B213D9C5D0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Journal!$A$5:$HI$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Journal!$B:$D,Journal!$1:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Journal!$A$1:$D$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>Insérer les lignes au-dessus de celle-ci !</t>
   </si>
@@ -294,6 +294,21 @@
   </si>
   <si>
     <t>Documentation</t>
+  </si>
+  <si>
+    <t>Relecture de la codebase</t>
+  </si>
+  <si>
+    <t>Relecture de la documentation</t>
+  </si>
+  <si>
+    <t>ça avance à la vitesse de la lumière, je ne pense pas en avoir encore pour 20h de travail et ça me rassure grandement</t>
+  </si>
+  <si>
+    <t>Sysprep… Je déteste Microsoft et ça semble se péréniser plus le temps passe…</t>
+  </si>
+  <si>
+    <t>Guide utilisateur</t>
   </si>
 </sst>
 </file>
@@ -403,7 +418,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -582,11 +597,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -635,12 +687,44 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -652,22 +736,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -679,12 +747,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -707,18 +779,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -727,6 +787,10 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -735,99 +799,39 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <strike val="0"/>
@@ -1365,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1"/>
@@ -1376,39 +1380,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="45"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
       <c r="D2" s="4">
         <v>157443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="41"/>
+      <c r="C4" s="15"/>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
@@ -1417,309 +1421,345 @@
       <c r="A6" s="38">
         <v>46153</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="18"/>
+      <c r="C7" s="19"/>
       <c r="D7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="24"/>
+      <c r="B8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="18"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="24"/>
+      <c r="B10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="18"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="18"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="16"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="2" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="9">
-        <f>SUM(D6:D14)</f>
+      <c r="D13" s="7">
+        <f>SUM(D6:D12)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16"/>
-      <c r="B16" s="21" t="s">
+    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="24"/>
+      <c r="B14" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23"/>
-    </row>
-    <row r="17" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="15">
+      <c r="C14" s="42"/>
+      <c r="D14" s="43"/>
+    </row>
+    <row r="15" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="23">
         <v>46154</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="7">
+      <c r="C15" s="19"/>
+      <c r="D15" s="8">
         <v>0.5</v>
       </c>
     </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="24"/>
+      <c r="B16" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="8">
+        <v>2.5</v>
+      </c>
+    </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="16"/>
-      <c r="B18" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="18"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="19"/>
       <c r="D18" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="16"/>
-      <c r="B20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="8">
+      <c r="A19" s="24"/>
+      <c r="B19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="7">
+        <f>SUM(D15:D18)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="24"/>
+      <c r="B20" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="42"/>
+      <c r="D20" s="43"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="23">
+        <v>46157</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="24"/>
+      <c r="B22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="16"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="48"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="16"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="8"/>
-    </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="8"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="16"/>
-      <c r="B24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="9">
-        <f>SUM(D17:D23)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16"/>
-      <c r="B25" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="23"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="15">
-        <v>46157</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="18"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="19"/>
       <c r="D26" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="18"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="19"/>
       <c r="D27" s="8">
         <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="16"/>
-      <c r="B28" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="18"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="19"/>
       <c r="D28" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="44"/>
+      <c r="B29" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="47"/>
+      <c r="D29" s="45">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="24"/>
+      <c r="B30" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="32"/>
+      <c r="D30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="24"/>
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="7">
+        <f>SUM(D21:D30)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="24"/>
+      <c r="B32" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="42"/>
+      <c r="D32" s="43"/>
+    </row>
+    <row r="33" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="23">
+        <v>46160</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="32"/>
+      <c r="D33" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="16"/>
-      <c r="B29" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="8">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="24"/>
+      <c r="B34" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="16"/>
-      <c r="B30" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="8">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="24"/>
+      <c r="B35" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="24"/>
+      <c r="B36" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="16"/>
-      <c r="B31" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="16"/>
-      <c r="B34" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="16"/>
-      <c r="B35" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="8">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="24"/>
+      <c r="B37" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="16"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="8"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="16"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="8"/>
-    </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="16"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="8"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="16"/>
+      <c r="A39" s="24"/>
       <c r="B39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1727,773 +1767,629 @@
         <v>5</v>
       </c>
       <c r="D39" s="9">
-        <f>SUM(D26:D38)</f>
+        <f>SUM(D33:D38)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="16"/>
-      <c r="B40" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="22"/>
-      <c r="D40" s="23"/>
-    </row>
-    <row r="41" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15">
-        <v>46160</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="8">
+    <row r="40" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="28"/>
+      <c r="B40" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="34"/>
+      <c r="D40" s="35"/>
+    </row>
+    <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="23">
+        <v>46161</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="24"/>
+      <c r="B42" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="16"/>
-      <c r="B42" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="16"/>
-      <c r="B43" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" s="18"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="19"/>
       <c r="D43" s="8">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="16"/>
-      <c r="B44" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="8">
+      <c r="A44" s="24"/>
+      <c r="B44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="9">
+        <f>SUM(D41:D43)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="28"/>
+      <c r="B45" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="35"/>
+    </row>
+    <row r="46" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="23">
+        <v>46163</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="30"/>
+      <c r="D46" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="24"/>
+      <c r="B47" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="30"/>
+      <c r="D47" s="8">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="24"/>
+      <c r="B48" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="24"/>
+      <c r="B49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="9">
+        <f>SUM(D46:D48)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="28"/>
+      <c r="B50" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="34"/>
+      <c r="D50" s="35"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="23">
+        <v>46164</v>
+      </c>
+      <c r="B51" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="40"/>
+      <c r="D51" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="16"/>
-      <c r="B45" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="8">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="24"/>
+      <c r="B52" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="24"/>
+      <c r="B53" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="32"/>
+      <c r="D53" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="24"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="8"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="24"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="8"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="24"/>
+      <c r="B56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="9">
+        <f>SUM(D51:D55)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="28"/>
+      <c r="B57" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="34"/>
+      <c r="D57" s="35"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="23">
+        <v>46171</v>
+      </c>
+      <c r="B58" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C58" s="30"/>
+      <c r="D58" s="7">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="16"/>
-      <c r="B46" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C46" s="18"/>
-      <c r="D46" s="8">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="24"/>
+      <c r="B59" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="16"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="8"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="16"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="8"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="16"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="8"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="16"/>
-      <c r="B50" s="2" t="s">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="24"/>
+      <c r="B60" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="24"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="24"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="8"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="24"/>
+      <c r="B63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="9">
-        <f>SUM(D41:D46)</f>
+      <c r="D63" s="9">
+        <f>SUM(D58:D62)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="31"/>
-      <c r="B51" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="30"/>
-    </row>
-    <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="15">
-        <v>46161</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="18"/>
-      <c r="D52" s="7">
+    <row r="64" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="28"/>
+      <c r="B64" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C64" s="34"/>
+      <c r="D64" s="35"/>
+    </row>
+    <row r="65" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="23">
+        <v>46174</v>
+      </c>
+      <c r="B65" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65" s="40"/>
+      <c r="D65" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="24"/>
+      <c r="B66" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="19"/>
+      <c r="D66" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="24"/>
+      <c r="B67" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" s="19"/>
+      <c r="D67" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="24"/>
+      <c r="B68" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C68" s="19"/>
+      <c r="D68" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="18"/>
-      <c r="D53" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="16"/>
-      <c r="B54" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" s="18"/>
-      <c r="D54" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="16"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="8"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="16"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="16"/>
-      <c r="B57" s="2" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="24"/>
+      <c r="B69" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="24"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="8"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="24"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="8"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="24"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="8"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="24"/>
+      <c r="B73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D57" s="9">
-        <f>SUM(D52:D56)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="31"/>
-      <c r="B58" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C58" s="29"/>
-      <c r="D58" s="30"/>
-    </row>
-    <row r="59" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="15">
-        <v>46163</v>
-      </c>
-      <c r="B59" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" s="33"/>
-      <c r="D59" s="7">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="16"/>
-      <c r="B60" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="8">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="16"/>
-      <c r="B61" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="18"/>
-      <c r="D61" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="16"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="8"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="16"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="8"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="16"/>
-      <c r="B64" s="2" t="s">
+      <c r="D73" s="9">
+        <f>SUM(D65:D72)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="24"/>
+      <c r="B74" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C74" s="26"/>
+      <c r="D74" s="27"/>
+    </row>
+    <row r="75" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="23">
+        <v>46175</v>
+      </c>
+      <c r="B75" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" s="40"/>
+      <c r="D75" s="7"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="24"/>
+      <c r="B76" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="8"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="24"/>
+      <c r="B77" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="8"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="24"/>
+      <c r="B78" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" s="8"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="24"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="8"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="24"/>
+      <c r="B80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D64" s="9">
-        <f>SUM(D59:D63)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="31"/>
-      <c r="B65" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="30"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="15">
-        <v>46164</v>
-      </c>
-      <c r="B66" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C66" s="37"/>
-      <c r="D66" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="16"/>
-      <c r="B67" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C67" s="18"/>
-      <c r="D67" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="16"/>
-      <c r="B68" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C68" s="27"/>
-      <c r="D68" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="16"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="8"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="16"/>
-      <c r="B70" s="34"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="8"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="16"/>
-      <c r="B71" s="2" t="s">
+      <c r="D80" s="9">
+        <f>SUM(D75:D79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="28"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="34"/>
+      <c r="D81" s="35"/>
+    </row>
+    <row r="82" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="23">
+        <v>46178</v>
+      </c>
+      <c r="B82" s="39"/>
+      <c r="C82" s="40"/>
+      <c r="D82" s="7"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="24"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="8"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="24"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="8"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="24"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="19"/>
+      <c r="D85" s="8"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="24"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="8"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="24"/>
+      <c r="B87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D71" s="9">
-        <f>SUM(D66:D70)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="31"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="30"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="15">
-        <v>46171</v>
-      </c>
-      <c r="B73" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C73" s="33"/>
-      <c r="D73" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="16"/>
-      <c r="B74" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C74" s="18"/>
-      <c r="D74" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="16"/>
-      <c r="B75" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="18"/>
-      <c r="D75" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="16"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="8"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="16"/>
-      <c r="B77" s="34"/>
-      <c r="C77" s="35"/>
-      <c r="D77" s="8"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="16"/>
-      <c r="B78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="9">
-        <f>SUM(D73:D77)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="31"/>
-      <c r="B79" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C79" s="29"/>
-      <c r="D79" s="30"/>
-    </row>
-    <row r="80" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="15">
-        <v>46174</v>
-      </c>
-      <c r="B80" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C80" s="37"/>
-      <c r="D80" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="18"/>
-      <c r="D81" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="16"/>
-      <c r="B82" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C82" s="18"/>
-      <c r="D82" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="16"/>
-      <c r="B83" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="18"/>
-      <c r="D83" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="16"/>
-      <c r="B84" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" s="18"/>
-      <c r="D84" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="16"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="8"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="16"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="8"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="16"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="8"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="16"/>
-      <c r="B88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D88" s="9">
-        <f>SUM(D80:D87)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="16"/>
-      <c r="B89" s="21"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="23"/>
-    </row>
-    <row r="90" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="15">
-        <v>46175</v>
-      </c>
-      <c r="B90" s="36"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="7"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="16"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="8"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="16"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="8"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="16"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="8"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="16"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="8"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="16"/>
-      <c r="B95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="9">
-        <f>SUM(D90:D94)</f>
+      <c r="D87" s="9">
+        <f>SUM(D82:D86)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="31"/>
-      <c r="B96" s="28"/>
-      <c r="C96" s="29"/>
-      <c r="D96" s="30"/>
-    </row>
-    <row r="97" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="15">
-        <v>46178</v>
-      </c>
-      <c r="B97" s="36"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="7"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="16"/>
-      <c r="B98" s="17"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="8"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="16"/>
-      <c r="B99" s="17"/>
-      <c r="C99" s="18"/>
-      <c r="D99" s="8"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="16"/>
-      <c r="B100" s="17"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="8"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="16"/>
-      <c r="B101" s="17"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="8"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="16"/>
-      <c r="B102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="9">
-        <f>SUM(D97:D101)</f>
+    <row r="88" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="28"/>
+      <c r="B88" s="33"/>
+      <c r="C88" s="34"/>
+      <c r="D88" s="35"/>
+    </row>
+    <row r="89" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="11"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="12">
+        <f>D13+D19+D31+D39+D44+D49+D56+D63+D73+D80+D87</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="22" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="31"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="29"/>
-      <c r="D103" s="30"/>
-    </row>
-    <row r="104" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="11"/>
-      <c r="B104" s="10"/>
-      <c r="C104" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D104" s="12">
-        <f>D15+D24+D39+D50+D57+D64+D71+D78+D88+D95+D102</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B105" s="46"/>
-      <c r="C105" s="46"/>
-      <c r="D105" s="46"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="103">
+  <mergeCells count="88">
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="A58:A64"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A82:A88"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="A75:A81"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B81:D81"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="A51:A57"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A17:A25"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A41:A51"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:A40"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="A52:A58"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A41:A45"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A6:A16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="A80:A89"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B89:D89"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A66:A72"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A97:A103"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="A90:A96"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B96:D96"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="A26:A40"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B79:D79"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D15 D17:D20 D22:D24 D26">
-    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="En cours">
+  <conditionalFormatting sqref="D21 D6:D13 D15:D19">
+    <cfRule type="containsText" dxfId="15" priority="24" operator="containsText" text="En cours">
       <formula>NOT(ISERROR(SEARCH("En cours",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D26 D6:D15 D17:D20 D22:D24">
-    <cfRule type="containsText" dxfId="18" priority="23" operator="containsText" text="Terminé">
+  <conditionalFormatting sqref="D21 D6:D13 D15:D19">
+    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="Terminé">
       <formula>NOT(ISERROR(SEARCH("Terminé",D6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D26:D39 D41:D50">
-    <cfRule type="containsText" dxfId="17" priority="3" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D26)))</formula>
+  <conditionalFormatting sqref="D21:D31 D33:D39 D41:D44 D46:D49">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D26)))</formula>
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D21)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D52:D57">
-    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D52)))</formula>
+  <conditionalFormatting sqref="D51:D56">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D52)))</formula>
+    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D51)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D59:D64">
-    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D59)))</formula>
+  <conditionalFormatting sqref="D58:D63">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D58)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D59)))</formula>
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D58)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D66:D71">
-    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D66)))</formula>
+  <conditionalFormatting sqref="D65:D73">
+    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D65)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D66)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D65)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D73:D78">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D73)))</formula>
+  <conditionalFormatting sqref="D75:D80">
+    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D75)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D73)))</formula>
+    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D75)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D80:D88">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D80)))</formula>
+  <conditionalFormatting sqref="D82:D87">
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
+      <formula>NOT(ISERROR(SEARCH("Terminé",D82)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D80)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
+      <formula>NOT(ISERROR(SEARCH("En cours",D82)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D90:D95">
-    <cfRule type="containsText" dxfId="5" priority="13" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D90)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="14" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D90)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D97:D102">
-    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D97)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D97)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D104">
+  <conditionalFormatting sqref="D89">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Terminé">
-      <formula>NOT(ISERROR(SEARCH("Terminé",D104)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Terminé",D89)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="En cours">
-      <formula>NOT(ISERROR(SEARCH("En cours",D104)))</formula>
+      <formula>NOT(ISERROR(SEARCH("En cours",D89)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -2505,8 +2401,8 @@
     <oddFooter>&amp;L&amp;8&amp;F&amp;R&amp;8Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
-    <brk id="65" max="16383" man="1"/>
-    <brk id="104" max="3" man="1"/>
+    <brk id="50" max="16383" man="1"/>
+    <brk id="89" max="3" man="1"/>
   </rowBreaks>
   <legacyDrawingHF r:id="rId2"/>
 </worksheet>
